--- a/crop_timeline.xlsx
+++ b/crop_timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D98506C-0DCB-5346-A0FF-357CB225A789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8834D98-98F7-FD44-AFE7-6DD359C51687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46260" yWindow="-4580" windowWidth="19200" windowHeight="19540" firstSheet="1" activeTab="4" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
+    <workbookView xWindow="46260" yWindow="-4580" windowWidth="19200" windowHeight="19540" firstSheet="5" activeTab="10" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_stage" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,11 @@
     <sheet name="pest_ins" sheetId="6" r:id="rId6"/>
     <sheet name="disease_fun" sheetId="7" r:id="rId7"/>
     <sheet name="fertilizer" sheetId="8" r:id="rId8"/>
-    <sheet name="crop_ref" sheetId="10" r:id="rId9"/>
-    <sheet name="ref" sheetId="9" r:id="rId10"/>
+    <sheet name="weed_matrix" sheetId="11" r:id="rId9"/>
+    <sheet name="insect_matrix" sheetId="12" r:id="rId10"/>
+    <sheet name="disease_matrix" sheetId="13" r:id="rId11"/>
+    <sheet name="crop_ref" sheetId="10" r:id="rId12"/>
+    <sheet name="ref" sheetId="9" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">crop_disease!$A$1:$H$19</definedName>
@@ -51,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3981" uniqueCount="914">
   <si>
     <t>crop_id</t>
   </si>
@@ -2766,6 +2769,35 @@
   </si>
   <si>
     <t>efficiency</t>
+  </si>
+  <si>
+    <t>crop</t>
+  </si>
+  <si>
+    <t>weed_name</t>
+  </si>
+  <si>
+    <t>insect_name</t>
+  </si>
+  <si>
+    <t>disease_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">butachlor
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bispyribac-sodium
+</t>
+  </si>
+  <si>
+    <t>Cyhalofop-butyl</t>
+  </si>
+  <si>
+    <t>Fenoxaprop-P-ethyl</t>
+  </si>
+  <si>
+    <t>Imidacroprid</t>
   </si>
 </sst>
 </file>
@@ -2828,7 +2860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2842,6 +2874,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3839,6 +3872,1718 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B2AF58-9C39-C24F-9CCB-B09BE479FA00}">
+  <dimension ref="A1:D85"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>907</v>
+      </c>
+      <c r="D1" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>339</v>
+      </c>
+      <c r="C13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>913</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>913</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>913</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>913</v>
+      </c>
+      <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>913</v>
+      </c>
+      <c r="C18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>913</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>913</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>913</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>913</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>913</v>
+      </c>
+      <c r="C24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>913</v>
+      </c>
+      <c r="C25" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" t="s">
+        <v>344</v>
+      </c>
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>344</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>344</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>344</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>344</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s">
+        <v>344</v>
+      </c>
+      <c r="C31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s">
+        <v>344</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>344</v>
+      </c>
+      <c r="C34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" t="s">
+        <v>344</v>
+      </c>
+      <c r="C35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>344</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>344</v>
+      </c>
+      <c r="C37" t="s">
+        <v>188</v>
+      </c>
+      <c r="D37" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>836</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>836</v>
+      </c>
+      <c r="C39" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>836</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>836</v>
+      </c>
+      <c r="C41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>836</v>
+      </c>
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>836</v>
+      </c>
+      <c r="C43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>836</v>
+      </c>
+      <c r="C44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>836</v>
+      </c>
+      <c r="C45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>836</v>
+      </c>
+      <c r="C46" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>836</v>
+      </c>
+      <c r="C47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
+        <v>836</v>
+      </c>
+      <c r="C48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" t="s">
+        <v>836</v>
+      </c>
+      <c r="C49" t="s">
+        <v>188</v>
+      </c>
+      <c r="D49" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" t="s">
+        <v>724</v>
+      </c>
+      <c r="C50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" t="s">
+        <v>724</v>
+      </c>
+      <c r="C51" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" t="s">
+        <v>724</v>
+      </c>
+      <c r="C52" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" t="s">
+        <v>724</v>
+      </c>
+      <c r="C53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" t="s">
+        <v>724</v>
+      </c>
+      <c r="C54" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" t="s">
+        <v>724</v>
+      </c>
+      <c r="C55" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" t="s">
+        <v>724</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" t="s">
+        <v>724</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>724</v>
+      </c>
+      <c r="C58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>724</v>
+      </c>
+      <c r="C59" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
+        <v>724</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" t="s">
+        <v>724</v>
+      </c>
+      <c r="C61" t="s">
+        <v>188</v>
+      </c>
+      <c r="D61" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>526</v>
+      </c>
+      <c r="C62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" t="s">
+        <v>526</v>
+      </c>
+      <c r="C63" t="s">
+        <v>103</v>
+      </c>
+      <c r="D63" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>526</v>
+      </c>
+      <c r="C64" t="s">
+        <v>107</v>
+      </c>
+      <c r="D64" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" t="s">
+        <v>526</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" t="s">
+        <v>526</v>
+      </c>
+      <c r="C66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>526</v>
+      </c>
+      <c r="C67" t="s">
+        <v>52</v>
+      </c>
+      <c r="D67" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>526</v>
+      </c>
+      <c r="C68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D68" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>526</v>
+      </c>
+      <c r="C69" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>526</v>
+      </c>
+      <c r="C70" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>526</v>
+      </c>
+      <c r="C71" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" t="s">
+        <v>526</v>
+      </c>
+      <c r="C72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" t="s">
+        <v>526</v>
+      </c>
+      <c r="C73" t="s">
+        <v>188</v>
+      </c>
+      <c r="D73" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s">
+        <v>523</v>
+      </c>
+      <c r="C74" t="s">
+        <v>47</v>
+      </c>
+      <c r="D74" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" t="s">
+        <v>523</v>
+      </c>
+      <c r="C75" t="s">
+        <v>103</v>
+      </c>
+      <c r="D75" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" t="s">
+        <v>523</v>
+      </c>
+      <c r="C76" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" t="s">
+        <v>523</v>
+      </c>
+      <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" t="s">
+        <v>523</v>
+      </c>
+      <c r="C78" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" t="s">
+        <v>523</v>
+      </c>
+      <c r="C79" t="s">
+        <v>52</v>
+      </c>
+      <c r="D79" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" t="s">
+        <v>523</v>
+      </c>
+      <c r="C80" t="s">
+        <v>51</v>
+      </c>
+      <c r="D80" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" t="s">
+        <v>523</v>
+      </c>
+      <c r="C81" t="s">
+        <v>49</v>
+      </c>
+      <c r="D81" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" t="s">
+        <v>523</v>
+      </c>
+      <c r="C82" t="s">
+        <v>116</v>
+      </c>
+      <c r="D82" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" t="s">
+        <v>523</v>
+      </c>
+      <c r="C83" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>44</v>
+      </c>
+      <c r="B84" t="s">
+        <v>523</v>
+      </c>
+      <c r="C84" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>44</v>
+      </c>
+      <c r="B85" t="s">
+        <v>523</v>
+      </c>
+      <c r="C85" t="s">
+        <v>188</v>
+      </c>
+      <c r="D85" t="s">
+        <v>901</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7B04602A-ED65-2749-962E-3DC6595F0751}">
+          <x14:formula1>
+            <xm:f>ref!$A$15:$A$19</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D234</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE4948BD-084B-8347-838E-A472E2BE2EE4}">
+          <x14:formula1>
+            <xm:f>ref!$E$2:$E$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C85</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147BC320-B632-D74D-97A3-1CF199D5F3D3}">
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>398</v>
+      </c>
+      <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>400</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>400</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>400</v>
+      </c>
+      <c r="C14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>400</v>
+      </c>
+      <c r="C16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>400</v>
+      </c>
+      <c r="C17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>401</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>401</v>
+      </c>
+      <c r="C21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>401</v>
+      </c>
+      <c r="C22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>401</v>
+      </c>
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>401</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>401</v>
+      </c>
+      <c r="C25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" t="s">
+        <v>401</v>
+      </c>
+      <c r="C26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>401</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>401</v>
+      </c>
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>901</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70C46D36-18B3-2944-B985-DC30327C6176}">
+          <x14:formula1>
+            <xm:f>ref!$A$15:$A$19</xm:f>
+          </x14:formula1>
+          <xm:sqref>D1:D28</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A64ED2-38E5-DF44-8359-DC945C6EA1B1}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD323E38-B5EE-7946-941F-1D3A439D6394}">
   <dimension ref="A1:O479"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -15069,71 +16814,2296 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A64ED2-38E5-DF44-8359-DC945C6EA1B1}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D926F36-D19F-454B-BF3B-05DFDA75FE19}">
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.1640625" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="C1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>906</v>
+      </c>
+      <c r="E1" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
+        <v>315</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>315</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>315</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>315</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>315</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="D23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>315</v>
+      </c>
+      <c r="C25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C27" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>315</v>
+      </c>
+      <c r="C28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" t="s">
+        <v>338</v>
+      </c>
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" t="s">
+        <v>338</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s">
+        <v>315</v>
+      </c>
+      <c r="C32" t="s">
+        <v>338</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>315</v>
+      </c>
+      <c r="C33" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>315</v>
+      </c>
+      <c r="C34" t="s">
+        <v>338</v>
+      </c>
+      <c r="D34" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" t="s">
+        <v>316</v>
+      </c>
+      <c r="C35" t="s">
+        <v>910</v>
+      </c>
+      <c r="D35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>316</v>
+      </c>
+      <c r="C36" t="s">
+        <v>910</v>
+      </c>
+      <c r="D36" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>316</v>
+      </c>
+      <c r="C37" t="s">
+        <v>910</v>
+      </c>
+      <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>316</v>
+      </c>
+      <c r="C38" t="s">
+        <v>910</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>316</v>
+      </c>
+      <c r="C39" t="s">
+        <v>910</v>
+      </c>
+      <c r="D39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>316</v>
+      </c>
+      <c r="C40" t="s">
+        <v>910</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>316</v>
+      </c>
+      <c r="C41" t="s">
+        <v>910</v>
+      </c>
+      <c r="D41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>316</v>
+      </c>
+      <c r="C42" t="s">
+        <v>910</v>
+      </c>
+      <c r="D42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>316</v>
+      </c>
+      <c r="C43" t="s">
+        <v>910</v>
+      </c>
+      <c r="D43" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C44" t="s">
+        <v>910</v>
+      </c>
+      <c r="D44" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>316</v>
+      </c>
+      <c r="C45" t="s">
+        <v>910</v>
+      </c>
+      <c r="D45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C46" t="s">
+        <v>330</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>316</v>
+      </c>
+      <c r="C47" t="s">
+        <v>330</v>
+      </c>
+      <c r="D47" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
+        <v>316</v>
+      </c>
+      <c r="C48" t="s">
+        <v>330</v>
+      </c>
+      <c r="D48" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" t="s">
+        <v>316</v>
+      </c>
+      <c r="C49" t="s">
+        <v>330</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" t="s">
+        <v>316</v>
+      </c>
+      <c r="C50" t="s">
+        <v>330</v>
+      </c>
+      <c r="D50" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" t="s">
+        <v>316</v>
+      </c>
+      <c r="C51" t="s">
+        <v>330</v>
+      </c>
+      <c r="D51" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" t="s">
+        <v>316</v>
+      </c>
+      <c r="C52" t="s">
+        <v>330</v>
+      </c>
+      <c r="D52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" t="s">
+        <v>316</v>
+      </c>
+      <c r="C53" t="s">
+        <v>330</v>
+      </c>
+      <c r="D53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" t="s">
+        <v>316</v>
+      </c>
+      <c r="C54" t="s">
+        <v>330</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" t="s">
+        <v>316</v>
+      </c>
+      <c r="C55" t="s">
+        <v>330</v>
+      </c>
+      <c r="D55" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" t="s">
+        <v>316</v>
+      </c>
+      <c r="C56" t="s">
+        <v>330</v>
+      </c>
+      <c r="D56" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" t="s">
+        <v>316</v>
+      </c>
+      <c r="C57" t="s">
+        <v>745</v>
+      </c>
+      <c r="D57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>316</v>
+      </c>
+      <c r="C58" t="s">
+        <v>745</v>
+      </c>
+      <c r="D58" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>316</v>
+      </c>
+      <c r="C59" t="s">
+        <v>745</v>
+      </c>
+      <c r="D59" t="s">
+        <v>65</v>
+      </c>
+      <c r="E59" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
+        <v>316</v>
+      </c>
+      <c r="C60" t="s">
+        <v>745</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" t="s">
+        <v>316</v>
+      </c>
+      <c r="C61" t="s">
+        <v>745</v>
+      </c>
+      <c r="D61" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>316</v>
+      </c>
+      <c r="C62" t="s">
+        <v>745</v>
+      </c>
+      <c r="D62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" t="s">
+        <v>316</v>
+      </c>
+      <c r="C63" t="s">
+        <v>745</v>
+      </c>
+      <c r="D63" t="s">
+        <v>83</v>
+      </c>
+      <c r="E63" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" t="s">
+        <v>745</v>
+      </c>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" t="s">
+        <v>316</v>
+      </c>
+      <c r="C65" t="s">
+        <v>745</v>
+      </c>
+      <c r="D65" t="s">
+        <v>91</v>
+      </c>
+      <c r="E65" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" t="s">
+        <v>316</v>
+      </c>
+      <c r="C66" t="s">
+        <v>745</v>
+      </c>
+      <c r="D66" t="s">
+        <v>94</v>
+      </c>
+      <c r="E66" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>316</v>
+      </c>
+      <c r="C67" t="s">
+        <v>745</v>
+      </c>
+      <c r="D67" t="s">
+        <v>97</v>
+      </c>
+      <c r="E67" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>316</v>
+      </c>
+      <c r="C68" t="s">
+        <v>495</v>
+      </c>
+      <c r="D68" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>316</v>
+      </c>
+      <c r="C69" t="s">
+        <v>495</v>
+      </c>
+      <c r="D69" t="s">
+        <v>60</v>
+      </c>
+      <c r="E69" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>316</v>
+      </c>
+      <c r="C70" t="s">
+        <v>495</v>
+      </c>
+      <c r="D70" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>316</v>
+      </c>
+      <c r="C71" t="s">
+        <v>495</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" t="s">
+        <v>316</v>
+      </c>
+      <c r="C72" t="s">
+        <v>495</v>
+      </c>
+      <c r="D72" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" t="s">
+        <v>316</v>
+      </c>
+      <c r="C73" t="s">
+        <v>495</v>
+      </c>
+      <c r="D73" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s">
+        <v>316</v>
+      </c>
+      <c r="C74" t="s">
+        <v>495</v>
+      </c>
+      <c r="D74" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" t="s">
+        <v>316</v>
+      </c>
+      <c r="C75" t="s">
+        <v>495</v>
+      </c>
+      <c r="D75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" t="s">
+        <v>316</v>
+      </c>
+      <c r="C76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D76" t="s">
+        <v>91</v>
+      </c>
+      <c r="E76" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" t="s">
+        <v>316</v>
+      </c>
+      <c r="C77" t="s">
+        <v>495</v>
+      </c>
+      <c r="D77" t="s">
+        <v>94</v>
+      </c>
+      <c r="E77" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" t="s">
+        <v>316</v>
+      </c>
+      <c r="C78" t="s">
+        <v>495</v>
+      </c>
+      <c r="D78" t="s">
+        <v>97</v>
+      </c>
+      <c r="E78" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" t="s">
+        <v>316</v>
+      </c>
+      <c r="C79" t="s">
+        <v>911</v>
+      </c>
+      <c r="D79" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" t="s">
+        <v>316</v>
+      </c>
+      <c r="C80" t="s">
+        <v>911</v>
+      </c>
+      <c r="D80" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" t="s">
+        <v>316</v>
+      </c>
+      <c r="C81" t="s">
+        <v>911</v>
+      </c>
+      <c r="D81" t="s">
+        <v>65</v>
+      </c>
+      <c r="E81" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" t="s">
+        <v>316</v>
+      </c>
+      <c r="C82" t="s">
+        <v>911</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" t="s">
+        <v>316</v>
+      </c>
+      <c r="C83" t="s">
+        <v>911</v>
+      </c>
+      <c r="D83" t="s">
+        <v>71</v>
+      </c>
+      <c r="E83" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>44</v>
+      </c>
+      <c r="B84" t="s">
+        <v>316</v>
+      </c>
+      <c r="C84" t="s">
+        <v>911</v>
+      </c>
+      <c r="D84" t="s">
+        <v>78</v>
+      </c>
+      <c r="E84" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>44</v>
+      </c>
+      <c r="B85" t="s">
+        <v>316</v>
+      </c>
+      <c r="C85" t="s">
+        <v>911</v>
+      </c>
+      <c r="D85" t="s">
+        <v>83</v>
+      </c>
+      <c r="E85" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>44</v>
+      </c>
+      <c r="B86" t="s">
+        <v>316</v>
+      </c>
+      <c r="C86" t="s">
+        <v>911</v>
+      </c>
+      <c r="D86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>44</v>
+      </c>
+      <c r="B87" t="s">
+        <v>316</v>
+      </c>
+      <c r="C87" t="s">
+        <v>911</v>
+      </c>
+      <c r="D87" t="s">
+        <v>91</v>
+      </c>
+      <c r="E87" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>44</v>
+      </c>
+      <c r="B88" t="s">
+        <v>316</v>
+      </c>
+      <c r="C88" t="s">
+        <v>911</v>
+      </c>
+      <c r="D88" t="s">
+        <v>94</v>
+      </c>
+      <c r="E88" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>44</v>
+      </c>
+      <c r="B89" t="s">
+        <v>316</v>
+      </c>
+      <c r="C89" t="s">
+        <v>911</v>
+      </c>
+      <c r="D89" t="s">
+        <v>97</v>
+      </c>
+      <c r="E89" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>44</v>
+      </c>
+      <c r="B90" t="s">
+        <v>316</v>
+      </c>
+      <c r="C90" t="s">
+        <v>912</v>
+      </c>
+      <c r="D90" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B91" t="s">
+        <v>316</v>
+      </c>
+      <c r="C91" t="s">
+        <v>912</v>
+      </c>
+      <c r="D91" t="s">
+        <v>60</v>
+      </c>
+      <c r="E91" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>44</v>
+      </c>
+      <c r="B92" t="s">
+        <v>316</v>
+      </c>
+      <c r="C92" t="s">
+        <v>912</v>
+      </c>
+      <c r="D92" t="s">
+        <v>65</v>
+      </c>
+      <c r="E92" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>44</v>
+      </c>
+      <c r="B93" t="s">
+        <v>316</v>
+      </c>
+      <c r="C93" t="s">
+        <v>912</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>44</v>
+      </c>
+      <c r="B94" t="s">
+        <v>316</v>
+      </c>
+      <c r="C94" t="s">
+        <v>912</v>
+      </c>
+      <c r="D94" t="s">
+        <v>71</v>
+      </c>
+      <c r="E94" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>44</v>
+      </c>
+      <c r="B95" t="s">
+        <v>316</v>
+      </c>
+      <c r="C95" t="s">
+        <v>912</v>
+      </c>
+      <c r="D95" t="s">
+        <v>78</v>
+      </c>
+      <c r="E95" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>44</v>
+      </c>
+      <c r="B96" t="s">
+        <v>316</v>
+      </c>
+      <c r="C96" t="s">
+        <v>912</v>
+      </c>
+      <c r="D96" t="s">
+        <v>83</v>
+      </c>
+      <c r="E96" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>44</v>
+      </c>
+      <c r="B97" t="s">
+        <v>316</v>
+      </c>
+      <c r="C97" t="s">
+        <v>912</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>44</v>
+      </c>
+      <c r="B98" t="s">
+        <v>316</v>
+      </c>
+      <c r="C98" t="s">
+        <v>912</v>
+      </c>
+      <c r="D98" t="s">
+        <v>91</v>
+      </c>
+      <c r="E98" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>44</v>
+      </c>
+      <c r="B99" t="s">
+        <v>316</v>
+      </c>
+      <c r="C99" t="s">
+        <v>912</v>
+      </c>
+      <c r="D99" t="s">
+        <v>94</v>
+      </c>
+      <c r="E99" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>44</v>
+      </c>
+      <c r="B100" t="s">
+        <v>316</v>
+      </c>
+      <c r="C100" t="s">
+        <v>912</v>
+      </c>
+      <c r="D100" t="s">
+        <v>97</v>
+      </c>
+      <c r="E100" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>44</v>
+      </c>
+      <c r="B101" t="s">
+        <v>317</v>
+      </c>
+      <c r="C101" t="s">
+        <v>330</v>
+      </c>
+      <c r="D101" t="s">
+        <v>58</v>
+      </c>
+      <c r="E101" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>44</v>
+      </c>
+      <c r="B102" t="s">
+        <v>317</v>
+      </c>
+      <c r="C102" t="s">
+        <v>330</v>
+      </c>
+      <c r="D102" t="s">
+        <v>60</v>
+      </c>
+      <c r="E102" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>44</v>
+      </c>
+      <c r="B103" t="s">
+        <v>317</v>
+      </c>
+      <c r="C103" t="s">
+        <v>330</v>
+      </c>
+      <c r="D103" t="s">
+        <v>65</v>
+      </c>
+      <c r="E103" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>44</v>
+      </c>
+      <c r="B104" t="s">
+        <v>317</v>
+      </c>
+      <c r="C104" t="s">
+        <v>330</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>44</v>
+      </c>
+      <c r="B105" t="s">
+        <v>317</v>
+      </c>
+      <c r="C105" t="s">
+        <v>330</v>
+      </c>
+      <c r="D105" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>44</v>
+      </c>
+      <c r="B106" t="s">
+        <v>317</v>
+      </c>
+      <c r="C106" t="s">
+        <v>330</v>
+      </c>
+      <c r="D106" t="s">
+        <v>78</v>
+      </c>
+      <c r="E106" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>44</v>
+      </c>
+      <c r="B107" t="s">
+        <v>317</v>
+      </c>
+      <c r="C107" t="s">
+        <v>330</v>
+      </c>
+      <c r="D107" t="s">
+        <v>83</v>
+      </c>
+      <c r="E107" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>44</v>
+      </c>
+      <c r="B108" t="s">
+        <v>317</v>
+      </c>
+      <c r="C108" t="s">
+        <v>330</v>
+      </c>
+      <c r="D108" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>44</v>
+      </c>
+      <c r="B109" t="s">
+        <v>317</v>
+      </c>
+      <c r="C109" t="s">
+        <v>330</v>
+      </c>
+      <c r="D109" t="s">
+        <v>91</v>
+      </c>
+      <c r="E109" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>44</v>
+      </c>
+      <c r="B110" t="s">
+        <v>317</v>
+      </c>
+      <c r="C110" t="s">
+        <v>330</v>
+      </c>
+      <c r="D110" t="s">
+        <v>94</v>
+      </c>
+      <c r="E110" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>44</v>
+      </c>
+      <c r="B111" t="s">
+        <v>317</v>
+      </c>
+      <c r="C111" t="s">
+        <v>330</v>
+      </c>
+      <c r="D111" t="s">
+        <v>97</v>
+      </c>
+      <c r="E111" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>44</v>
+      </c>
+      <c r="B112" t="s">
+        <v>317</v>
+      </c>
+      <c r="C112" t="s">
+        <v>745</v>
+      </c>
+      <c r="D112" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>44</v>
+      </c>
+      <c r="B113" t="s">
+        <v>317</v>
+      </c>
+      <c r="C113" t="s">
+        <v>745</v>
+      </c>
+      <c r="D113" t="s">
+        <v>60</v>
+      </c>
+      <c r="E113" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>44</v>
+      </c>
+      <c r="B114" t="s">
+        <v>317</v>
+      </c>
+      <c r="C114" t="s">
+        <v>745</v>
+      </c>
+      <c r="D114" t="s">
+        <v>65</v>
+      </c>
+      <c r="E114" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>44</v>
+      </c>
+      <c r="B115" t="s">
+        <v>317</v>
+      </c>
+      <c r="C115" t="s">
+        <v>745</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>44</v>
+      </c>
+      <c r="B116" t="s">
+        <v>317</v>
+      </c>
+      <c r="C116" t="s">
+        <v>745</v>
+      </c>
+      <c r="D116" t="s">
+        <v>71</v>
+      </c>
+      <c r="E116" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>44</v>
+      </c>
+      <c r="B117" t="s">
+        <v>317</v>
+      </c>
+      <c r="C117" t="s">
+        <v>745</v>
+      </c>
+      <c r="D117" t="s">
+        <v>78</v>
+      </c>
+      <c r="E117" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>44</v>
+      </c>
+      <c r="B118" t="s">
+        <v>317</v>
+      </c>
+      <c r="C118" t="s">
+        <v>745</v>
+      </c>
+      <c r="D118" t="s">
+        <v>83</v>
+      </c>
+      <c r="E118" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>44</v>
+      </c>
+      <c r="B119" t="s">
+        <v>317</v>
+      </c>
+      <c r="C119" t="s">
+        <v>745</v>
+      </c>
+      <c r="D119" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" t="s">
+        <v>317</v>
+      </c>
+      <c r="C120" t="s">
+        <v>745</v>
+      </c>
+      <c r="D120" t="s">
+        <v>91</v>
+      </c>
+      <c r="E120" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>44</v>
+      </c>
+      <c r="B121" t="s">
+        <v>317</v>
+      </c>
+      <c r="C121" t="s">
+        <v>745</v>
+      </c>
+      <c r="D121" t="s">
+        <v>94</v>
+      </c>
+      <c r="E121" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>44</v>
+      </c>
+      <c r="B122" t="s">
+        <v>317</v>
+      </c>
+      <c r="C122" t="s">
+        <v>745</v>
+      </c>
+      <c r="D122" t="s">
+        <v>97</v>
+      </c>
+      <c r="E122" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>44</v>
+      </c>
+      <c r="B123" t="s">
+        <v>317</v>
+      </c>
+      <c r="C123" t="s">
+        <v>495</v>
+      </c>
+      <c r="D123" t="s">
+        <v>58</v>
+      </c>
+      <c r="E123" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>44</v>
+      </c>
+      <c r="B124" t="s">
+        <v>317</v>
+      </c>
+      <c r="C124" t="s">
+        <v>495</v>
+      </c>
+      <c r="D124" t="s">
+        <v>60</v>
+      </c>
+      <c r="E124" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>44</v>
+      </c>
+      <c r="B125" t="s">
+        <v>317</v>
+      </c>
+      <c r="C125" t="s">
+        <v>495</v>
+      </c>
+      <c r="D125" t="s">
+        <v>65</v>
+      </c>
+      <c r="E125" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>44</v>
+      </c>
+      <c r="B126" t="s">
+        <v>317</v>
+      </c>
+      <c r="C126" t="s">
+        <v>495</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>44</v>
+      </c>
+      <c r="B127" t="s">
+        <v>317</v>
+      </c>
+      <c r="C127" t="s">
+        <v>495</v>
+      </c>
+      <c r="D127" t="s">
+        <v>71</v>
+      </c>
+      <c r="E127" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>44</v>
+      </c>
+      <c r="B128" t="s">
+        <v>317</v>
+      </c>
+      <c r="C128" t="s">
+        <v>495</v>
+      </c>
+      <c r="D128" t="s">
+        <v>78</v>
+      </c>
+      <c r="E128" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>44</v>
+      </c>
+      <c r="B129" t="s">
+        <v>317</v>
+      </c>
+      <c r="C129" t="s">
+        <v>495</v>
+      </c>
+      <c r="D129" t="s">
+        <v>83</v>
+      </c>
+      <c r="E129" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>44</v>
+      </c>
+      <c r="B130" t="s">
+        <v>317</v>
+      </c>
+      <c r="C130" t="s">
+        <v>495</v>
+      </c>
+      <c r="D130" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>44</v>
+      </c>
+      <c r="B131" t="s">
+        <v>317</v>
+      </c>
+      <c r="C131" t="s">
+        <v>495</v>
+      </c>
+      <c r="D131" t="s">
+        <v>91</v>
+      </c>
+      <c r="E131" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>44</v>
+      </c>
+      <c r="B132" t="s">
+        <v>317</v>
+      </c>
+      <c r="C132" t="s">
+        <v>495</v>
+      </c>
+      <c r="D132" t="s">
+        <v>94</v>
+      </c>
+      <c r="E132" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B133" t="s">
+        <v>317</v>
+      </c>
+      <c r="C133" t="s">
+        <v>495</v>
+      </c>
+      <c r="D133" t="s">
+        <v>97</v>
+      </c>
+      <c r="E133" t="s">
+        <v>903</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{07402F78-40B4-DC45-9B62-9E379920F97B}">
+          <x14:formula1>
+            <xm:f>ref!$B$2:$B$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D133</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BB7ABDAF-6A61-AD4C-8BEE-21E3B4F4623A}">
+          <x14:formula1>
+            <xm:f>ref!$A$15:$A$19</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E340</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/crop_timeline.xlsx
+++ b/crop_timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167B47A3-DF8C-5F43-ACAA-F0288BFFA8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5123EFE3-412C-FF48-9511-1A4C8B8EAC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46260" yWindow="-5000" windowWidth="19200" windowHeight="19540" firstSheet="5" activeTab="10" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
+    <workbookView xWindow="40200" yWindow="-5200" windowWidth="22140" windowHeight="19540" firstSheet="3" activeTab="4" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_stage" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3981" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3983" uniqueCount="917">
   <si>
     <t>crop_id</t>
   </si>
@@ -2798,6 +2798,15 @@
   </si>
   <si>
     <t>Imidacroprid</t>
+  </si>
+  <si>
+    <t>effectiveness</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -3878,6 +3887,7 @@
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -3891,7 +3901,7 @@
         <v>907</v>
       </c>
       <c r="D1" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3905,7 +3915,7 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3919,7 +3929,7 @@
         <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3933,7 +3943,7 @@
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3947,7 +3957,7 @@
         <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3961,7 +3971,7 @@
         <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -3975,7 +3985,7 @@
         <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3989,7 +3999,7 @@
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4003,7 +4013,7 @@
         <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4017,7 +4027,7 @@
         <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4031,7 +4041,7 @@
         <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4045,7 +4055,7 @@
         <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4059,7 +4069,7 @@
         <v>188</v>
       </c>
       <c r="D13" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4073,7 +4083,7 @@
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4087,7 +4097,7 @@
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4101,7 +4111,7 @@
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4115,7 +4125,7 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -4129,7 +4139,7 @@
         <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4143,7 +4153,7 @@
         <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -4157,7 +4167,7 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -4171,7 +4181,7 @@
         <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4185,7 +4195,7 @@
         <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4199,7 +4209,7 @@
         <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4213,7 +4223,7 @@
         <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4227,7 +4237,7 @@
         <v>188</v>
       </c>
       <c r="D25" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4241,7 +4251,7 @@
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4255,7 +4265,7 @@
         <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4269,7 +4279,7 @@
         <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4283,7 +4293,7 @@
         <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4297,7 +4307,7 @@
         <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4311,7 +4321,7 @@
         <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4325,7 +4335,7 @@
         <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4339,7 +4349,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4353,7 +4363,7 @@
         <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4367,7 +4377,7 @@
         <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -4381,7 +4391,7 @@
         <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4395,7 +4405,7 @@
         <v>188</v>
       </c>
       <c r="D37" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4409,7 +4419,7 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4423,7 +4433,7 @@
         <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4437,7 +4447,7 @@
         <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4451,7 +4461,7 @@
         <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4465,7 +4475,7 @@
         <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4479,7 +4489,7 @@
         <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4493,7 +4503,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4507,7 +4517,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4521,7 +4531,7 @@
         <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4535,7 +4545,7 @@
         <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4549,7 +4559,7 @@
         <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4563,7 +4573,7 @@
         <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4577,7 +4587,7 @@
         <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4591,7 +4601,7 @@
         <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4605,7 +4615,7 @@
         <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4619,7 +4629,7 @@
         <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4633,7 +4643,7 @@
         <v>114</v>
       </c>
       <c r="D54" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -4647,7 +4657,7 @@
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -4661,7 +4671,7 @@
         <v>51</v>
       </c>
       <c r="D56" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4675,7 +4685,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4689,7 +4699,7 @@
         <v>116</v>
       </c>
       <c r="D58" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4703,7 +4713,7 @@
         <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4717,7 +4727,7 @@
         <v>120</v>
       </c>
       <c r="D60" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4731,7 +4741,7 @@
         <v>188</v>
       </c>
       <c r="D61" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4745,7 +4755,7 @@
         <v>47</v>
       </c>
       <c r="D62" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4759,7 +4769,7 @@
         <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4773,7 +4783,7 @@
         <v>107</v>
       </c>
       <c r="D64" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -4787,7 +4797,7 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -4801,7 +4811,7 @@
         <v>114</v>
       </c>
       <c r="D66" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -4815,7 +4825,7 @@
         <v>52</v>
       </c>
       <c r="D67" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -4829,7 +4839,7 @@
         <v>51</v>
       </c>
       <c r="D68" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -4843,7 +4853,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -4857,7 +4867,7 @@
         <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -4871,7 +4881,7 @@
         <v>118</v>
       </c>
       <c r="D71" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -4885,7 +4895,7 @@
         <v>120</v>
       </c>
       <c r="D72" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -4899,7 +4909,7 @@
         <v>188</v>
       </c>
       <c r="D73" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -4913,7 +4923,7 @@
         <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -4927,7 +4937,7 @@
         <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -4941,7 +4951,7 @@
         <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -4955,7 +4965,7 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -4969,7 +4979,7 @@
         <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -4983,7 +4993,7 @@
         <v>52</v>
       </c>
       <c r="D79" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -4997,7 +5007,7 @@
         <v>51</v>
       </c>
       <c r="D80" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -5011,7 +5021,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -5025,7 +5035,7 @@
         <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -5039,7 +5049,7 @@
         <v>118</v>
       </c>
       <c r="D83" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -5053,7 +5063,7 @@
         <v>120</v>
       </c>
       <c r="D84" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -5067,25 +5077,31 @@
         <v>188</v>
       </c>
       <c r="D85" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7B04602A-ED65-2749-962E-3DC6595F0751}">
           <x14:formula1>
             <xm:f>ref!$A$15:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D234</xm:sqref>
+          <xm:sqref>D86:D234</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE4948BD-084B-8347-838E-A472E2BE2EE4}">
           <x14:formula1>
             <xm:f>ref!$E$2:$E$13</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C85</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{681353A4-3D9B-A94C-A91E-8C3DDA213310}">
+          <x14:formula1>
+            <xm:f>ref!$B$15:$B$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D85</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5101,6 +5117,7 @@
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -5114,7 +5131,7 @@
         <v>908</v>
       </c>
       <c r="D1" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5128,7 +5145,7 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -5142,7 +5159,7 @@
         <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -5156,7 +5173,7 @@
         <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -5170,7 +5187,7 @@
         <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -5184,7 +5201,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5198,7 +5215,7 @@
         <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5212,7 +5229,7 @@
         <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -5226,7 +5243,7 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -5240,7 +5257,7 @@
         <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -5254,7 +5271,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -5268,7 +5285,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -5282,7 +5299,7 @@
         <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -5296,7 +5313,7 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -5310,7 +5327,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -5324,7 +5341,7 @@
         <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -5338,7 +5355,7 @@
         <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -5352,7 +5369,7 @@
         <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -5366,7 +5383,7 @@
         <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -5380,7 +5397,7 @@
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -5394,7 +5411,7 @@
         <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -5408,7 +5425,7 @@
         <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -5422,7 +5439,7 @@
         <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -5436,7 +5453,7 @@
         <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -5450,7 +5467,7 @@
         <v>142</v>
       </c>
       <c r="D25" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -5464,7 +5481,7 @@
         <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -5478,7 +5495,7 @@
         <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -5492,19 +5509,25 @@
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70C46D36-18B3-2944-B985-DC30327C6176}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DD3B365A-2F99-D94E-9405-60FA09AFE980}">
           <x14:formula1>
             <xm:f>ref!$A$15:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D28</xm:sqref>
+          <xm:sqref>D3:D28</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9924F720-6D83-424F-BC5A-D6348EC3C52F}">
+          <x14:formula1>
+            <xm:f>ref!$B$15:$B$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5973,6 +5996,9 @@
       <c r="A15" t="s">
         <v>899</v>
       </c>
+      <c r="B15" t="s">
+        <v>915</v>
+      </c>
       <c r="K15" t="s">
         <v>164</v>
       </c>
@@ -5989,6 +6015,9 @@
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>900</v>
+      </c>
+      <c r="B16" t="s">
+        <v>916</v>
       </c>
       <c r="K16" t="s">
         <v>185</v>
@@ -16837,7 +16866,7 @@
         <v>906</v>
       </c>
       <c r="E1" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -16854,7 +16883,7 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -16871,7 +16900,7 @@
         <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -16888,7 +16917,7 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -16905,7 +16934,7 @@
         <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -16922,7 +16951,7 @@
         <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -16939,7 +16968,7 @@
         <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -16956,7 +16985,7 @@
         <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -16973,7 +17002,7 @@
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -16990,7 +17019,7 @@
         <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -17007,7 +17036,7 @@
         <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -17024,7 +17053,7 @@
         <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -17041,7 +17070,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -17058,7 +17087,7 @@
         <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -17075,7 +17104,7 @@
         <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -17092,7 +17121,7 @@
         <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -17109,7 +17138,7 @@
         <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -17126,7 +17155,7 @@
         <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -17143,7 +17172,7 @@
         <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -17160,7 +17189,7 @@
         <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -17177,7 +17206,7 @@
         <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -17194,7 +17223,7 @@
         <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -17211,7 +17240,7 @@
         <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -17228,7 +17257,7 @@
         <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -17245,7 +17274,7 @@
         <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -17262,7 +17291,7 @@
         <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -17279,7 +17308,7 @@
         <v>69</v>
       </c>
       <c r="E27" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -17296,7 +17325,7 @@
         <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -17313,7 +17342,7 @@
         <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -17330,7 +17359,7 @@
         <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -17347,7 +17376,7 @@
         <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -17364,7 +17393,7 @@
         <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -17381,7 +17410,7 @@
         <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -17398,7 +17427,7 @@
         <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17415,7 +17444,7 @@
         <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -17432,7 +17461,7 @@
         <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -17449,7 +17478,7 @@
         <v>65</v>
       </c>
       <c r="E37" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -17466,7 +17495,7 @@
         <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -17483,7 +17512,7 @@
         <v>71</v>
       </c>
       <c r="E39" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -17500,7 +17529,7 @@
         <v>78</v>
       </c>
       <c r="E40" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -17517,7 +17546,7 @@
         <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -17534,7 +17563,7 @@
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -17551,7 +17580,7 @@
         <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -17568,7 +17597,7 @@
         <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -17585,7 +17614,7 @@
         <v>97</v>
       </c>
       <c r="E45" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -17602,7 +17631,7 @@
         <v>58</v>
       </c>
       <c r="E46" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -17619,7 +17648,7 @@
         <v>60</v>
       </c>
       <c r="E47" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -17636,7 +17665,7 @@
         <v>65</v>
       </c>
       <c r="E48" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -17653,7 +17682,7 @@
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -17670,7 +17699,7 @@
         <v>71</v>
       </c>
       <c r="E50" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -17687,7 +17716,7 @@
         <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -17704,7 +17733,7 @@
         <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -17721,7 +17750,7 @@
         <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -17738,7 +17767,7 @@
         <v>91</v>
       </c>
       <c r="E54" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -17755,7 +17784,7 @@
         <v>94</v>
       </c>
       <c r="E55" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -17772,7 +17801,7 @@
         <v>97</v>
       </c>
       <c r="E56" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -17789,7 +17818,7 @@
         <v>58</v>
       </c>
       <c r="E57" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -17806,7 +17835,7 @@
         <v>60</v>
       </c>
       <c r="E58" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -17823,7 +17852,7 @@
         <v>65</v>
       </c>
       <c r="E59" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -17840,7 +17869,7 @@
         <v>69</v>
       </c>
       <c r="E60" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -17857,7 +17886,7 @@
         <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -17874,7 +17903,7 @@
         <v>78</v>
       </c>
       <c r="E62" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -17891,7 +17920,7 @@
         <v>83</v>
       </c>
       <c r="E63" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -17908,7 +17937,7 @@
         <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -17925,7 +17954,7 @@
         <v>91</v>
       </c>
       <c r="E65" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -17942,7 +17971,7 @@
         <v>94</v>
       </c>
       <c r="E66" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -17959,7 +17988,7 @@
         <v>97</v>
       </c>
       <c r="E67" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -17976,7 +18005,7 @@
         <v>58</v>
       </c>
       <c r="E68" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -17993,7 +18022,7 @@
         <v>60</v>
       </c>
       <c r="E69" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -18010,7 +18039,7 @@
         <v>65</v>
       </c>
       <c r="E70" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -18027,7 +18056,7 @@
         <v>69</v>
       </c>
       <c r="E71" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -18044,7 +18073,7 @@
         <v>71</v>
       </c>
       <c r="E72" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -18061,7 +18090,7 @@
         <v>78</v>
       </c>
       <c r="E73" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -18078,7 +18107,7 @@
         <v>83</v>
       </c>
       <c r="E74" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -18095,7 +18124,7 @@
         <v>17</v>
       </c>
       <c r="E75" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -18112,7 +18141,7 @@
         <v>91</v>
       </c>
       <c r="E76" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -18129,7 +18158,7 @@
         <v>94</v>
       </c>
       <c r="E77" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -18146,7 +18175,7 @@
         <v>97</v>
       </c>
       <c r="E78" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -18163,7 +18192,7 @@
         <v>58</v>
       </c>
       <c r="E79" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -18180,7 +18209,7 @@
         <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -18197,7 +18226,7 @@
         <v>65</v>
       </c>
       <c r="E81" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -18214,7 +18243,7 @@
         <v>69</v>
       </c>
       <c r="E82" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -18231,7 +18260,7 @@
         <v>71</v>
       </c>
       <c r="E83" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -18248,7 +18277,7 @@
         <v>78</v>
       </c>
       <c r="E84" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -18265,7 +18294,7 @@
         <v>83</v>
       </c>
       <c r="E85" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -18282,7 +18311,7 @@
         <v>17</v>
       </c>
       <c r="E86" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -18299,7 +18328,7 @@
         <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -18316,7 +18345,7 @@
         <v>94</v>
       </c>
       <c r="E88" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -18333,7 +18362,7 @@
         <v>97</v>
       </c>
       <c r="E89" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -18350,7 +18379,7 @@
         <v>58</v>
       </c>
       <c r="E90" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -18367,7 +18396,7 @@
         <v>60</v>
       </c>
       <c r="E91" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -18384,7 +18413,7 @@
         <v>65</v>
       </c>
       <c r="E92" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -18401,7 +18430,7 @@
         <v>69</v>
       </c>
       <c r="E93" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -18418,7 +18447,7 @@
         <v>71</v>
       </c>
       <c r="E94" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -18435,7 +18464,7 @@
         <v>78</v>
       </c>
       <c r="E95" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -18452,7 +18481,7 @@
         <v>83</v>
       </c>
       <c r="E96" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -18469,7 +18498,7 @@
         <v>17</v>
       </c>
       <c r="E97" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -18486,7 +18515,7 @@
         <v>91</v>
       </c>
       <c r="E98" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -18503,7 +18532,7 @@
         <v>94</v>
       </c>
       <c r="E99" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -18520,7 +18549,7 @@
         <v>97</v>
       </c>
       <c r="E100" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -18537,7 +18566,7 @@
         <v>58</v>
       </c>
       <c r="E101" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -18554,7 +18583,7 @@
         <v>60</v>
       </c>
       <c r="E102" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -18571,7 +18600,7 @@
         <v>65</v>
       </c>
       <c r="E103" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -18588,7 +18617,7 @@
         <v>69</v>
       </c>
       <c r="E104" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -18605,7 +18634,7 @@
         <v>71</v>
       </c>
       <c r="E105" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -18622,7 +18651,7 @@
         <v>78</v>
       </c>
       <c r="E106" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -18639,7 +18668,7 @@
         <v>83</v>
       </c>
       <c r="E107" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -18656,7 +18685,7 @@
         <v>17</v>
       </c>
       <c r="E108" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -18673,7 +18702,7 @@
         <v>91</v>
       </c>
       <c r="E109" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -18690,7 +18719,7 @@
         <v>94</v>
       </c>
       <c r="E110" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -18707,7 +18736,7 @@
         <v>97</v>
       </c>
       <c r="E111" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -18724,7 +18753,7 @@
         <v>58</v>
       </c>
       <c r="E112" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -18741,7 +18770,7 @@
         <v>60</v>
       </c>
       <c r="E113" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -18758,7 +18787,7 @@
         <v>65</v>
       </c>
       <c r="E114" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -18775,7 +18804,7 @@
         <v>69</v>
       </c>
       <c r="E115" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -18792,7 +18821,7 @@
         <v>71</v>
       </c>
       <c r="E116" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -18809,7 +18838,7 @@
         <v>78</v>
       </c>
       <c r="E117" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -18826,7 +18855,7 @@
         <v>83</v>
       </c>
       <c r="E118" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -18843,7 +18872,7 @@
         <v>17</v>
       </c>
       <c r="E119" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -18860,7 +18889,7 @@
         <v>91</v>
       </c>
       <c r="E120" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -18877,7 +18906,7 @@
         <v>94</v>
       </c>
       <c r="E121" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -18894,7 +18923,7 @@
         <v>97</v>
       </c>
       <c r="E122" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -18911,7 +18940,7 @@
         <v>58</v>
       </c>
       <c r="E123" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -18928,7 +18957,7 @@
         <v>60</v>
       </c>
       <c r="E124" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -18945,7 +18974,7 @@
         <v>65</v>
       </c>
       <c r="E125" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -18962,7 +18991,7 @@
         <v>69</v>
       </c>
       <c r="E126" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -18979,7 +19008,7 @@
         <v>71</v>
       </c>
       <c r="E127" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -18996,7 +19025,7 @@
         <v>78</v>
       </c>
       <c r="E128" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -19013,7 +19042,7 @@
         <v>83</v>
       </c>
       <c r="E129" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -19030,7 +19059,7 @@
         <v>17</v>
       </c>
       <c r="E130" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -19047,7 +19076,7 @@
         <v>91</v>
       </c>
       <c r="E131" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -19064,7 +19093,7 @@
         <v>94</v>
       </c>
       <c r="E132" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -19081,14 +19110,14 @@
         <v>97</v>
       </c>
       <c r="E133" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{07402F78-40B4-DC45-9B62-9E379920F97B}">
           <x14:formula1>
             <xm:f>ref!$B$2:$B$12</xm:f>
@@ -19099,7 +19128,13 @@
           <x14:formula1>
             <xm:f>ref!$A$15:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E340</xm:sqref>
+          <xm:sqref>E134:E340</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{29FA82CE-BF5C-A54C-A8D1-056AA986A90C}">
+          <x14:formula1>
+            <xm:f>ref!$B$15:$B$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E133</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/crop_timeline.xlsx
+++ b/crop_timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5123EFE3-412C-FF48-9511-1A4C8B8EAC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B908F44F-82DE-3145-ABDB-F3808646A9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40200" yWindow="-5200" windowWidth="22140" windowHeight="19540" firstSheet="3" activeTab="4" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
+    <workbookView xWindow="40200" yWindow="-5200" windowWidth="22140" windowHeight="19540" firstSheet="3" activeTab="8" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_stage" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3983" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="915">
   <si>
     <t>crop_id</t>
   </si>
@@ -2801,12 +2801,6 @@
   </si>
   <si>
     <t>effectiveness</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -3915,7 +3909,7 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3929,7 +3923,7 @@
         <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3943,7 +3937,7 @@
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3957,7 +3951,7 @@
         <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3971,7 +3965,7 @@
         <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -3985,7 +3979,7 @@
         <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3999,7 +3993,7 @@
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4013,7 +4007,7 @@
         <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4027,7 +4021,7 @@
         <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4041,7 +4035,7 @@
         <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4055,7 +4049,7 @@
         <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4069,7 +4063,7 @@
         <v>188</v>
       </c>
       <c r="D13" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4083,7 +4077,7 @@
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4097,7 +4091,7 @@
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4111,7 +4105,7 @@
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4125,7 +4119,7 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -4139,7 +4133,7 @@
         <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4153,7 +4147,7 @@
         <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -4167,7 +4161,7 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -4181,7 +4175,7 @@
         <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4195,7 +4189,7 @@
         <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4209,7 +4203,7 @@
         <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4223,7 +4217,7 @@
         <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4237,7 +4231,7 @@
         <v>188</v>
       </c>
       <c r="D25" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4251,7 +4245,7 @@
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4265,7 +4259,7 @@
         <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4279,7 +4273,7 @@
         <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4293,7 +4287,7 @@
         <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4307,7 +4301,7 @@
         <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4321,7 +4315,7 @@
         <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4335,7 +4329,7 @@
         <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4349,7 +4343,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4363,7 +4357,7 @@
         <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4377,7 +4371,7 @@
         <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -4391,7 +4385,7 @@
         <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4405,7 +4399,7 @@
         <v>188</v>
       </c>
       <c r="D37" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4419,7 +4413,7 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4433,7 +4427,7 @@
         <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4447,7 +4441,7 @@
         <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4461,7 +4455,7 @@
         <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4475,7 +4469,7 @@
         <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4489,7 +4483,7 @@
         <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4503,7 +4497,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4517,7 +4511,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4531,7 +4525,7 @@
         <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4545,7 +4539,7 @@
         <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4559,7 +4553,7 @@
         <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4573,7 +4567,7 @@
         <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4587,7 +4581,7 @@
         <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4601,7 +4595,7 @@
         <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4615,7 +4609,7 @@
         <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4629,7 +4623,7 @@
         <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4643,7 +4637,7 @@
         <v>114</v>
       </c>
       <c r="D54" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -4657,7 +4651,7 @@
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -4671,7 +4665,7 @@
         <v>51</v>
       </c>
       <c r="D56" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4685,7 +4679,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4699,7 +4693,7 @@
         <v>116</v>
       </c>
       <c r="D58" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4713,7 +4707,7 @@
         <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4727,7 +4721,7 @@
         <v>120</v>
       </c>
       <c r="D60" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4741,7 +4735,7 @@
         <v>188</v>
       </c>
       <c r="D61" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4755,7 +4749,7 @@
         <v>47</v>
       </c>
       <c r="D62" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4769,7 +4763,7 @@
         <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4783,7 +4777,7 @@
         <v>107</v>
       </c>
       <c r="D64" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -4797,7 +4791,7 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -4811,7 +4805,7 @@
         <v>114</v>
       </c>
       <c r="D66" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -4825,7 +4819,7 @@
         <v>52</v>
       </c>
       <c r="D67" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -4839,7 +4833,7 @@
         <v>51</v>
       </c>
       <c r="D68" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -4853,7 +4847,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -4867,7 +4861,7 @@
         <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -4881,7 +4875,7 @@
         <v>118</v>
       </c>
       <c r="D71" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -4895,7 +4889,7 @@
         <v>120</v>
       </c>
       <c r="D72" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -4909,7 +4903,7 @@
         <v>188</v>
       </c>
       <c r="D73" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -4923,7 +4917,7 @@
         <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -4937,7 +4931,7 @@
         <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -4951,7 +4945,7 @@
         <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -4965,7 +4959,7 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -4979,7 +4973,7 @@
         <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -4993,7 +4987,7 @@
         <v>52</v>
       </c>
       <c r="D79" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -5007,7 +5001,7 @@
         <v>51</v>
       </c>
       <c r="D80" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -5021,7 +5015,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -5035,7 +5029,7 @@
         <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -5049,7 +5043,7 @@
         <v>118</v>
       </c>
       <c r="D83" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -5063,7 +5057,7 @@
         <v>120</v>
       </c>
       <c r="D84" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -5077,7 +5071,7 @@
         <v>188</v>
       </c>
       <c r="D85" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -5097,9 +5091,9 @@
           </x14:formula1>
           <xm:sqref>C2:C85</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{681353A4-3D9B-A94C-A91E-8C3DDA213310}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{85D83087-7CDD-F641-B7DD-713627F193AF}">
           <x14:formula1>
-            <xm:f>ref!$B$15:$B$16</xm:f>
+            <xm:f>ref!$B$15:$B$17</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D85</xm:sqref>
         </x14:dataValidation>
@@ -5145,7 +5139,7 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -5159,7 +5153,7 @@
         <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -5173,7 +5167,7 @@
         <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -5187,7 +5181,7 @@
         <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -5201,7 +5195,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5215,7 +5209,7 @@
         <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5229,7 +5223,7 @@
         <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -5243,7 +5237,7 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -5257,7 +5251,7 @@
         <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -5271,7 +5265,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -5285,7 +5279,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -5299,7 +5293,7 @@
         <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -5313,7 +5307,7 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -5327,7 +5321,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -5341,7 +5335,7 @@
         <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -5355,7 +5349,7 @@
         <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -5369,7 +5363,7 @@
         <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -5383,7 +5377,7 @@
         <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -5397,7 +5391,7 @@
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -5411,7 +5405,7 @@
         <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -5425,7 +5419,7 @@
         <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -5439,7 +5433,7 @@
         <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -5453,7 +5447,7 @@
         <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -5467,7 +5461,7 @@
         <v>142</v>
       </c>
       <c r="D25" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -5481,7 +5475,7 @@
         <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -5495,7 +5489,7 @@
         <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -5509,25 +5503,19 @@
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DD3B365A-2F99-D94E-9405-60FA09AFE980}">
-          <x14:formula1>
-            <xm:f>ref!$A$15:$A$19</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3:D28</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9924F720-6D83-424F-BC5A-D6348EC3C52F}">
           <x14:formula1>
-            <xm:f>ref!$B$15:$B$16</xm:f>
+            <xm:f>ref!$B$15:$B$17</xm:f>
           </x14:formula1>
-          <xm:sqref>D2</xm:sqref>
+          <xm:sqref>D2:D28</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5997,7 +5985,7 @@
         <v>899</v>
       </c>
       <c r="B15" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="K15" t="s">
         <v>164</v>
@@ -6017,7 +6005,7 @@
         <v>900</v>
       </c>
       <c r="B16" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="K16" t="s">
         <v>185</v>
@@ -6035,6 +6023,9 @@
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>901</v>
+      </c>
+      <c r="B17" t="s">
+        <v>903</v>
       </c>
       <c r="K17" t="s">
         <v>186</v>
@@ -16883,7 +16874,7 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -16900,7 +16891,7 @@
         <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -16917,7 +16908,7 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -16934,7 +16925,7 @@
         <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -16951,7 +16942,7 @@
         <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -16968,7 +16959,7 @@
         <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -16985,7 +16976,7 @@
         <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -17002,7 +16993,7 @@
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -17019,7 +17010,7 @@
         <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -17036,7 +17027,7 @@
         <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -17053,7 +17044,7 @@
         <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -17070,7 +17061,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -17087,7 +17078,7 @@
         <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -17104,7 +17095,7 @@
         <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -17121,7 +17112,7 @@
         <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -17138,7 +17129,7 @@
         <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -17155,7 +17146,7 @@
         <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -17172,7 +17163,7 @@
         <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -17189,7 +17180,7 @@
         <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -17206,7 +17197,7 @@
         <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -17223,7 +17214,7 @@
         <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -17240,7 +17231,7 @@
         <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -17257,7 +17248,7 @@
         <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -17274,7 +17265,7 @@
         <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -17291,7 +17282,7 @@
         <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -17308,7 +17299,7 @@
         <v>69</v>
       </c>
       <c r="E27" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -17325,7 +17316,7 @@
         <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -17342,7 +17333,7 @@
         <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -17359,7 +17350,7 @@
         <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -17376,7 +17367,7 @@
         <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -17393,7 +17384,7 @@
         <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -17410,7 +17401,7 @@
         <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -17427,7 +17418,7 @@
         <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17444,7 +17435,7 @@
         <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -17461,7 +17452,7 @@
         <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -17478,7 +17469,7 @@
         <v>65</v>
       </c>
       <c r="E37" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -17495,7 +17486,7 @@
         <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -17512,7 +17503,7 @@
         <v>71</v>
       </c>
       <c r="E39" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -17529,7 +17520,7 @@
         <v>78</v>
       </c>
       <c r="E40" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -17546,7 +17537,7 @@
         <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -17563,7 +17554,7 @@
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -17580,7 +17571,7 @@
         <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -17597,7 +17588,7 @@
         <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -17614,7 +17605,7 @@
         <v>97</v>
       </c>
       <c r="E45" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -17631,7 +17622,7 @@
         <v>58</v>
       </c>
       <c r="E46" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -17648,7 +17639,7 @@
         <v>60</v>
       </c>
       <c r="E47" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -17665,7 +17656,7 @@
         <v>65</v>
       </c>
       <c r="E48" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -17682,7 +17673,7 @@
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -17699,7 +17690,7 @@
         <v>71</v>
       </c>
       <c r="E50" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -17716,7 +17707,7 @@
         <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -17733,7 +17724,7 @@
         <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -17750,7 +17741,7 @@
         <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -17767,7 +17758,7 @@
         <v>91</v>
       </c>
       <c r="E54" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -17784,7 +17775,7 @@
         <v>94</v>
       </c>
       <c r="E55" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -17801,7 +17792,7 @@
         <v>97</v>
       </c>
       <c r="E56" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -17818,7 +17809,7 @@
         <v>58</v>
       </c>
       <c r="E57" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -17835,7 +17826,7 @@
         <v>60</v>
       </c>
       <c r="E58" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -17852,7 +17843,7 @@
         <v>65</v>
       </c>
       <c r="E59" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -17869,7 +17860,7 @@
         <v>69</v>
       </c>
       <c r="E60" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -17886,7 +17877,7 @@
         <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -17903,7 +17894,7 @@
         <v>78</v>
       </c>
       <c r="E62" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -17920,7 +17911,7 @@
         <v>83</v>
       </c>
       <c r="E63" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -17937,7 +17928,7 @@
         <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -17954,7 +17945,7 @@
         <v>91</v>
       </c>
       <c r="E65" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -17971,7 +17962,7 @@
         <v>94</v>
       </c>
       <c r="E66" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -17988,7 +17979,7 @@
         <v>97</v>
       </c>
       <c r="E67" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -18005,7 +17996,7 @@
         <v>58</v>
       </c>
       <c r="E68" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -18022,7 +18013,7 @@
         <v>60</v>
       </c>
       <c r="E69" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -18039,7 +18030,7 @@
         <v>65</v>
       </c>
       <c r="E70" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -18056,7 +18047,7 @@
         <v>69</v>
       </c>
       <c r="E71" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -18073,7 +18064,7 @@
         <v>71</v>
       </c>
       <c r="E72" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -18090,7 +18081,7 @@
         <v>78</v>
       </c>
       <c r="E73" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -18107,7 +18098,7 @@
         <v>83</v>
       </c>
       <c r="E74" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -18124,7 +18115,7 @@
         <v>17</v>
       </c>
       <c r="E75" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -18141,7 +18132,7 @@
         <v>91</v>
       </c>
       <c r="E76" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -18158,7 +18149,7 @@
         <v>94</v>
       </c>
       <c r="E77" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -18175,7 +18166,7 @@
         <v>97</v>
       </c>
       <c r="E78" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -18192,7 +18183,7 @@
         <v>58</v>
       </c>
       <c r="E79" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -18209,7 +18200,7 @@
         <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -18226,7 +18217,7 @@
         <v>65</v>
       </c>
       <c r="E81" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -18243,7 +18234,7 @@
         <v>69</v>
       </c>
       <c r="E82" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -18260,7 +18251,7 @@
         <v>71</v>
       </c>
       <c r="E83" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -18277,7 +18268,7 @@
         <v>78</v>
       </c>
       <c r="E84" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -18294,7 +18285,7 @@
         <v>83</v>
       </c>
       <c r="E85" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -18311,7 +18302,7 @@
         <v>17</v>
       </c>
       <c r="E86" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -18328,7 +18319,7 @@
         <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -18345,7 +18336,7 @@
         <v>94</v>
       </c>
       <c r="E88" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -18362,7 +18353,7 @@
         <v>97</v>
       </c>
       <c r="E89" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -18379,7 +18370,7 @@
         <v>58</v>
       </c>
       <c r="E90" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -18396,7 +18387,7 @@
         <v>60</v>
       </c>
       <c r="E91" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -18413,7 +18404,7 @@
         <v>65</v>
       </c>
       <c r="E92" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -18430,7 +18421,7 @@
         <v>69</v>
       </c>
       <c r="E93" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -18447,7 +18438,7 @@
         <v>71</v>
       </c>
       <c r="E94" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -18464,7 +18455,7 @@
         <v>78</v>
       </c>
       <c r="E95" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -18481,7 +18472,7 @@
         <v>83</v>
       </c>
       <c r="E96" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -18498,7 +18489,7 @@
         <v>17</v>
       </c>
       <c r="E97" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -18515,7 +18506,7 @@
         <v>91</v>
       </c>
       <c r="E98" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -18532,7 +18523,7 @@
         <v>94</v>
       </c>
       <c r="E99" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -18549,7 +18540,7 @@
         <v>97</v>
       </c>
       <c r="E100" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -18566,7 +18557,7 @@
         <v>58</v>
       </c>
       <c r="E101" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -18583,7 +18574,7 @@
         <v>60</v>
       </c>
       <c r="E102" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -18600,7 +18591,7 @@
         <v>65</v>
       </c>
       <c r="E103" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -18617,7 +18608,7 @@
         <v>69</v>
       </c>
       <c r="E104" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -18634,7 +18625,7 @@
         <v>71</v>
       </c>
       <c r="E105" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -18651,7 +18642,7 @@
         <v>78</v>
       </c>
       <c r="E106" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -18668,7 +18659,7 @@
         <v>83</v>
       </c>
       <c r="E107" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -18685,7 +18676,7 @@
         <v>17</v>
       </c>
       <c r="E108" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -18702,7 +18693,7 @@
         <v>91</v>
       </c>
       <c r="E109" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -18719,7 +18710,7 @@
         <v>94</v>
       </c>
       <c r="E110" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -18736,7 +18727,7 @@
         <v>97</v>
       </c>
       <c r="E111" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -18753,7 +18744,7 @@
         <v>58</v>
       </c>
       <c r="E112" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -18770,7 +18761,7 @@
         <v>60</v>
       </c>
       <c r="E113" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -18787,7 +18778,7 @@
         <v>65</v>
       </c>
       <c r="E114" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -18804,7 +18795,7 @@
         <v>69</v>
       </c>
       <c r="E115" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -18821,7 +18812,7 @@
         <v>71</v>
       </c>
       <c r="E116" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -18838,7 +18829,7 @@
         <v>78</v>
       </c>
       <c r="E117" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -18855,7 +18846,7 @@
         <v>83</v>
       </c>
       <c r="E118" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -18872,7 +18863,7 @@
         <v>17</v>
       </c>
       <c r="E119" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -18889,7 +18880,7 @@
         <v>91</v>
       </c>
       <c r="E120" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -18906,7 +18897,7 @@
         <v>94</v>
       </c>
       <c r="E121" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -18923,7 +18914,7 @@
         <v>97</v>
       </c>
       <c r="E122" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -18940,7 +18931,7 @@
         <v>58</v>
       </c>
       <c r="E123" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -18957,7 +18948,7 @@
         <v>60</v>
       </c>
       <c r="E124" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -18974,7 +18965,7 @@
         <v>65</v>
       </c>
       <c r="E125" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -18991,7 +18982,7 @@
         <v>69</v>
       </c>
       <c r="E126" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -19008,7 +18999,7 @@
         <v>71</v>
       </c>
       <c r="E127" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -19025,7 +19016,7 @@
         <v>78</v>
       </c>
       <c r="E128" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -19042,7 +19033,7 @@
         <v>83</v>
       </c>
       <c r="E129" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -19059,7 +19050,7 @@
         <v>17</v>
       </c>
       <c r="E130" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -19076,7 +19067,7 @@
         <v>91</v>
       </c>
       <c r="E131" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -19093,7 +19084,7 @@
         <v>94</v>
       </c>
       <c r="E132" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -19110,7 +19101,7 @@
         <v>97</v>
       </c>
       <c r="E133" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -19130,9 +19121,9 @@
           </x14:formula1>
           <xm:sqref>E134:E340</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{29FA82CE-BF5C-A54C-A8D1-056AA986A90C}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5115C371-8CDD-9847-A531-5B97CE07BBB4}">
           <x14:formula1>
-            <xm:f>ref!$B$15:$B$16</xm:f>
+            <xm:f>ref!$B$15:$B$17</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E133</xm:sqref>
         </x14:dataValidation>

--- a/crop_timeline.xlsx
+++ b/crop_timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B908F44F-82DE-3145-ABDB-F3808646A9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEE2722-4AEC-8C48-9A88-00818734D429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40200" yWindow="-5200" windowWidth="22140" windowHeight="19540" firstSheet="3" activeTab="8" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
+    <workbookView xWindow="40200" yWindow="-5200" windowWidth="22140" windowHeight="19540" firstSheet="3" activeTab="12" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_stage" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="913">
   <si>
     <t>crop_id</t>
   </si>
@@ -2753,16 +2753,10 @@
     <t>rank</t>
   </si>
   <si>
-    <t>Excellent</t>
-  </si>
-  <si>
     <t>Effective</t>
   </si>
   <si>
     <t>Moderate</t>
-  </si>
-  <si>
-    <t>Poor</t>
   </si>
   <si>
     <t>Ineffective</t>
@@ -3886,16 +3880,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B1" t="s">
         <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3909,7 +3903,7 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3923,7 +3917,7 @@
         <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3937,7 +3931,7 @@
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3951,7 +3945,7 @@
         <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3965,7 +3959,7 @@
         <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -3979,7 +3973,7 @@
         <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3993,7 +3987,7 @@
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4007,7 +4001,7 @@
         <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4021,7 +4015,7 @@
         <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4035,7 +4029,7 @@
         <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4049,7 +4043,7 @@
         <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4063,7 +4057,7 @@
         <v>188</v>
       </c>
       <c r="D13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4071,13 +4065,13 @@
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C14" t="s">
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4085,13 +4079,13 @@
         <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4099,13 +4093,13 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C16" t="s">
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4113,13 +4107,13 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C17" t="s">
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -4127,13 +4121,13 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C18" t="s">
         <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4141,13 +4135,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C19" t="s">
         <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -4155,13 +4149,13 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C20" t="s">
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -4169,13 +4163,13 @@
         <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C21" t="s">
         <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4183,13 +4177,13 @@
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C22" t="s">
         <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4197,13 +4191,13 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C23" t="s">
         <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4211,13 +4205,13 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C24" t="s">
         <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4225,13 +4219,13 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C25" t="s">
         <v>188</v>
       </c>
       <c r="D25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4245,7 +4239,7 @@
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4259,7 +4253,7 @@
         <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4273,7 +4267,7 @@
         <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4287,7 +4281,7 @@
         <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4301,7 +4295,7 @@
         <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4315,7 +4309,7 @@
         <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4329,7 +4323,7 @@
         <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4343,7 +4337,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4357,7 +4351,7 @@
         <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4371,7 +4365,7 @@
         <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -4385,7 +4379,7 @@
         <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4399,7 +4393,7 @@
         <v>188</v>
       </c>
       <c r="D37" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4413,7 +4407,7 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4427,7 +4421,7 @@
         <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4441,7 +4435,7 @@
         <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4455,7 +4449,7 @@
         <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4469,7 +4463,7 @@
         <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4483,7 +4477,7 @@
         <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4497,7 +4491,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4511,7 +4505,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4525,7 +4519,7 @@
         <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4539,7 +4533,7 @@
         <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4553,7 +4547,7 @@
         <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4567,7 +4561,7 @@
         <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4581,7 +4575,7 @@
         <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4595,7 +4589,7 @@
         <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4609,7 +4603,7 @@
         <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4623,7 +4617,7 @@
         <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4637,7 +4631,7 @@
         <v>114</v>
       </c>
       <c r="D54" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -4651,7 +4645,7 @@
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -4665,7 +4659,7 @@
         <v>51</v>
       </c>
       <c r="D56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4679,7 +4673,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4693,7 +4687,7 @@
         <v>116</v>
       </c>
       <c r="D58" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4707,7 +4701,7 @@
         <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4721,7 +4715,7 @@
         <v>120</v>
       </c>
       <c r="D60" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4735,7 +4729,7 @@
         <v>188</v>
       </c>
       <c r="D61" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4749,7 +4743,7 @@
         <v>47</v>
       </c>
       <c r="D62" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4763,7 +4757,7 @@
         <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4777,7 +4771,7 @@
         <v>107</v>
       </c>
       <c r="D64" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -4791,7 +4785,7 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -4805,7 +4799,7 @@
         <v>114</v>
       </c>
       <c r="D66" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -4819,7 +4813,7 @@
         <v>52</v>
       </c>
       <c r="D67" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -4833,7 +4827,7 @@
         <v>51</v>
       </c>
       <c r="D68" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -4847,7 +4841,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -4861,7 +4855,7 @@
         <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -4875,7 +4869,7 @@
         <v>118</v>
       </c>
       <c r="D71" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -4889,7 +4883,7 @@
         <v>120</v>
       </c>
       <c r="D72" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -4903,7 +4897,7 @@
         <v>188</v>
       </c>
       <c r="D73" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -4917,7 +4911,7 @@
         <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -4931,7 +4925,7 @@
         <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -4945,7 +4939,7 @@
         <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -4959,7 +4953,7 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -4973,7 +4967,7 @@
         <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -4987,7 +4981,7 @@
         <v>52</v>
       </c>
       <c r="D79" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -5001,7 +4995,7 @@
         <v>51</v>
       </c>
       <c r="D80" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -5015,7 +5009,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -5029,7 +5023,7 @@
         <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -5043,7 +5037,7 @@
         <v>118</v>
       </c>
       <c r="D83" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -5057,7 +5051,7 @@
         <v>120</v>
       </c>
       <c r="D84" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -5071,7 +5065,7 @@
         <v>188</v>
       </c>
       <c r="D85" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -5116,16 +5110,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B1" t="s">
         <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5139,7 +5133,7 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -5153,7 +5147,7 @@
         <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -5167,7 +5161,7 @@
         <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -5181,7 +5175,7 @@
         <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -5195,7 +5189,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5209,7 +5203,7 @@
         <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5223,7 +5217,7 @@
         <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -5237,7 +5231,7 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -5251,7 +5245,7 @@
         <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -5265,7 +5259,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -5279,7 +5273,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -5293,7 +5287,7 @@
         <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -5307,7 +5301,7 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -5321,7 +5315,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -5335,7 +5329,7 @@
         <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -5349,7 +5343,7 @@
         <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -5363,7 +5357,7 @@
         <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -5377,7 +5371,7 @@
         <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -5391,7 +5385,7 @@
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -5405,7 +5399,7 @@
         <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -5419,7 +5413,7 @@
         <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -5433,7 +5427,7 @@
         <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -5447,7 +5441,7 @@
         <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -5461,7 +5455,7 @@
         <v>142</v>
       </c>
       <c r="D25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -5475,7 +5469,7 @@
         <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -5489,7 +5483,7 @@
         <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -5503,7 +5497,7 @@
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -5981,11 +5975,8 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>899</v>
-      </c>
-      <c r="B15" t="s">
-        <v>900</v>
       </c>
       <c r="K15" t="s">
         <v>164</v>
@@ -6001,11 +5992,8 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>900</v>
-      </c>
       <c r="B16" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="K16" t="s">
         <v>185</v>
@@ -6020,12 +6008,9 @@
         <v>441</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
         <v>901</v>
-      </c>
-      <c r="B17" t="s">
-        <v>903</v>
       </c>
       <c r="K17" t="s">
         <v>186</v>
@@ -6040,10 +6025,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>902</v>
-      </c>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K18" t="s">
         <v>187</v>
       </c>
@@ -6057,76 +6039,73 @@
         <v>443</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>903</v>
-      </c>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="L19" s="1"/>
       <c r="O19" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O20" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O21" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O22" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O23" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O24" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O25" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O26" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O27" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O28" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O29" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O30" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O31" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="O32" t="s">
         <v>457</v>
       </c>
@@ -11192,7 +11171,7 @@
         <v>212</v>
       </c>
       <c r="H1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -11218,7 +11197,7 @@
         <v>334</v>
       </c>
       <c r="H2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -11244,7 +11223,7 @@
         <v>334</v>
       </c>
       <c r="H3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -11270,7 +11249,7 @@
         <v>334</v>
       </c>
       <c r="H4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -11296,7 +11275,7 @@
         <v>334</v>
       </c>
       <c r="H5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -11322,7 +11301,7 @@
         <v>334</v>
       </c>
       <c r="H6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -11348,7 +11327,7 @@
         <v>334</v>
       </c>
       <c r="H7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -11374,7 +11353,7 @@
         <v>334</v>
       </c>
       <c r="H8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -11400,7 +11379,7 @@
         <v>334</v>
       </c>
       <c r="H9" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -11426,7 +11405,7 @@
         <v>333</v>
       </c>
       <c r="H10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -11452,7 +11431,7 @@
         <v>333</v>
       </c>
       <c r="H11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -11478,7 +11457,7 @@
         <v>333</v>
       </c>
       <c r="H12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -11504,7 +11483,7 @@
         <v>333</v>
       </c>
       <c r="H13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -11530,7 +11509,7 @@
         <v>333</v>
       </c>
       <c r="H14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -11556,7 +11535,7 @@
         <v>333</v>
       </c>
       <c r="H15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -11582,7 +11561,7 @@
         <v>333</v>
       </c>
       <c r="H16" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -11608,7 +11587,7 @@
         <v>333</v>
       </c>
       <c r="H17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -11634,7 +11613,7 @@
         <v>333</v>
       </c>
       <c r="H18" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -11660,7 +11639,7 @@
         <v>333</v>
       </c>
       <c r="H19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -11686,7 +11665,7 @@
         <v>332</v>
       </c>
       <c r="H20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -11712,7 +11691,7 @@
         <v>332</v>
       </c>
       <c r="H21" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -11738,7 +11717,7 @@
         <v>332</v>
       </c>
       <c r="H22" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -11764,7 +11743,7 @@
         <v>332</v>
       </c>
       <c r="H23" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -11790,7 +11769,7 @@
         <v>332</v>
       </c>
       <c r="H24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -11816,7 +11795,7 @@
         <v>332</v>
       </c>
       <c r="H25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -11842,7 +11821,7 @@
         <v>332</v>
       </c>
       <c r="H26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -11868,7 +11847,7 @@
         <v>332</v>
       </c>
       <c r="H27" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -11894,7 +11873,7 @@
         <v>332</v>
       </c>
       <c r="H28" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -11920,7 +11899,7 @@
         <v>332</v>
       </c>
       <c r="H29" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -11946,7 +11925,7 @@
         <v>329</v>
       </c>
       <c r="H30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -11972,7 +11951,7 @@
         <v>329</v>
       </c>
       <c r="H31" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -11998,7 +11977,7 @@
         <v>329</v>
       </c>
       <c r="H32" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -12024,7 +12003,7 @@
         <v>329</v>
       </c>
       <c r="H33" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -12050,7 +12029,7 @@
         <v>329</v>
       </c>
       <c r="H34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -12076,7 +12055,7 @@
         <v>329</v>
       </c>
       <c r="H35" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -12102,7 +12081,7 @@
         <v>329</v>
       </c>
       <c r="H36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -12128,7 +12107,7 @@
         <v>329</v>
       </c>
       <c r="H37" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -12154,7 +12133,7 @@
         <v>329</v>
       </c>
       <c r="H38" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -12180,7 +12159,7 @@
         <v>329</v>
       </c>
       <c r="H39" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -12206,7 +12185,7 @@
         <v>331</v>
       </c>
       <c r="H40" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -12232,7 +12211,7 @@
         <v>331</v>
       </c>
       <c r="H41" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -12258,7 +12237,7 @@
         <v>331</v>
       </c>
       <c r="H42" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -12284,7 +12263,7 @@
         <v>331</v>
       </c>
       <c r="H43" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -12310,7 +12289,7 @@
         <v>331</v>
       </c>
       <c r="H44" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -12336,7 +12315,7 @@
         <v>331</v>
       </c>
       <c r="H45" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -12362,7 +12341,7 @@
         <v>331</v>
       </c>
       <c r="H46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -12388,7 +12367,7 @@
         <v>331</v>
       </c>
       <c r="H47" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -12414,7 +12393,7 @@
         <v>331</v>
       </c>
       <c r="H48" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -12440,7 +12419,7 @@
         <v>331</v>
       </c>
       <c r="H49" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -12466,7 +12445,7 @@
         <v>331</v>
       </c>
       <c r="H50" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -12492,7 +12471,7 @@
         <v>331</v>
       </c>
       <c r="H51" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -12518,7 +12497,7 @@
         <v>331</v>
       </c>
       <c r="H52" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -12544,7 +12523,7 @@
         <v>331</v>
       </c>
       <c r="H53" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -12570,7 +12549,7 @@
         <v>331</v>
       </c>
       <c r="H54" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -12596,7 +12575,7 @@
         <v>331</v>
       </c>
       <c r="H55" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -12622,7 +12601,7 @@
         <v>331</v>
       </c>
       <c r="H56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -12648,7 +12627,7 @@
         <v>331</v>
       </c>
       <c r="H57" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -12674,7 +12653,7 @@
         <v>331</v>
       </c>
       <c r="H58" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -12700,7 +12679,7 @@
         <v>331</v>
       </c>
       <c r="H59" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -12726,7 +12705,7 @@
         <v>331</v>
       </c>
       <c r="H60" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -12752,7 +12731,7 @@
         <v>331</v>
       </c>
       <c r="H61" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -12778,7 +12757,7 @@
         <v>331</v>
       </c>
       <c r="H62" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -12804,7 +12783,7 @@
         <v>331</v>
       </c>
       <c r="H63" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -12830,7 +12809,7 @@
         <v>331</v>
       </c>
       <c r="H64" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -12856,7 +12835,7 @@
         <v>331</v>
       </c>
       <c r="H65" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -12882,7 +12861,7 @@
         <v>331</v>
       </c>
       <c r="H66" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -12908,7 +12887,7 @@
         <v>331</v>
       </c>
       <c r="H67" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -12934,7 +12913,7 @@
         <v>331</v>
       </c>
       <c r="H68" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -12960,7 +12939,7 @@
         <v>331</v>
       </c>
       <c r="H69" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -12986,7 +12965,7 @@
         <v>331</v>
       </c>
       <c r="H70" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -13012,7 +12991,7 @@
         <v>331</v>
       </c>
       <c r="H71" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -13038,7 +13017,7 @@
         <v>331</v>
       </c>
       <c r="H72" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -13064,7 +13043,7 @@
         <v>331</v>
       </c>
       <c r="H73" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -13090,7 +13069,7 @@
         <v>331</v>
       </c>
       <c r="H74" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -13116,7 +13095,7 @@
         <v>331</v>
       </c>
       <c r="H75" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -13142,7 +13121,7 @@
         <v>331</v>
       </c>
       <c r="H76" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -13168,7 +13147,7 @@
         <v>331</v>
       </c>
       <c r="H77" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -13194,7 +13173,7 @@
         <v>336</v>
       </c>
       <c r="H78" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -13220,7 +13199,7 @@
         <v>336</v>
       </c>
       <c r="H79" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -13246,7 +13225,7 @@
         <v>336</v>
       </c>
       <c r="H80" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -13272,7 +13251,7 @@
         <v>336</v>
       </c>
       <c r="H81" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -13298,7 +13277,7 @@
         <v>336</v>
       </c>
       <c r="H82" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -13324,7 +13303,7 @@
         <v>336</v>
       </c>
       <c r="H83" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -13350,7 +13329,7 @@
         <v>336</v>
       </c>
       <c r="H84" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -13376,7 +13355,7 @@
         <v>336</v>
       </c>
       <c r="H85" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -13402,7 +13381,7 @@
         <v>336</v>
       </c>
       <c r="H86" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -13430,7 +13409,7 @@
         <v>331</v>
       </c>
       <c r="H87" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -13458,7 +13437,7 @@
         <v>331</v>
       </c>
       <c r="H88" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -13486,7 +13465,7 @@
         <v>331</v>
       </c>
       <c r="H89" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -13514,7 +13493,7 @@
         <v>331</v>
       </c>
       <c r="H90" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -13542,7 +13521,7 @@
         <v>331</v>
       </c>
       <c r="H91" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -13570,7 +13549,7 @@
         <v>331</v>
       </c>
       <c r="H92" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -13598,7 +13577,7 @@
         <v>329</v>
       </c>
       <c r="H93" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -13626,7 +13605,7 @@
         <v>329</v>
       </c>
       <c r="H94" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -13654,7 +13633,7 @@
         <v>329</v>
       </c>
       <c r="H95" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -13682,7 +13661,7 @@
         <v>329</v>
       </c>
       <c r="H96" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -13710,7 +13689,7 @@
         <v>329</v>
       </c>
       <c r="H97" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -13738,7 +13717,7 @@
         <v>329</v>
       </c>
       <c r="H98" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -13766,7 +13745,7 @@
         <v>329</v>
       </c>
       <c r="H99" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -13992,9 +13971,9 @@
           </x14:formula1>
           <xm:sqref>D10:E63 D7:E8 D2:E5 E87:E109 D78:E81 D69:E72</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9697E08-3DD1-F149-B903-FE4DEE5B6CC4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D88844CE-4161-504D-BA50-F48AD7224935}">
           <x14:formula1>
-            <xm:f>ref!$A$15:$A$19</xm:f>
+            <xm:f>ref!$B$15:$B$17</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H99</xm:sqref>
         </x14:dataValidation>
@@ -14029,7 +14008,7 @@
         <v>213</v>
       </c>
       <c r="F1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -14049,7 +14028,7 @@
         <v>329</v>
       </c>
       <c r="F2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -14069,7 +14048,7 @@
         <v>341</v>
       </c>
       <c r="F3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -14089,7 +14068,7 @@
         <v>341</v>
       </c>
       <c r="F4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -14109,7 +14088,7 @@
         <v>341</v>
       </c>
       <c r="F5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -14129,7 +14108,7 @@
         <v>341</v>
       </c>
       <c r="F6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -14149,7 +14128,7 @@
         <v>346</v>
       </c>
       <c r="F7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -14189,7 +14168,7 @@
         <v>349</v>
       </c>
       <c r="F9" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -14209,7 +14188,7 @@
         <v>349</v>
       </c>
       <c r="F10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -14229,7 +14208,7 @@
         <v>352</v>
       </c>
       <c r="F11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -14249,7 +14228,7 @@
         <v>354</v>
       </c>
       <c r="F12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -14269,7 +14248,7 @@
         <v>354</v>
       </c>
       <c r="F13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -14289,7 +14268,7 @@
         <v>354</v>
       </c>
       <c r="F14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -14349,7 +14328,7 @@
         <v>346</v>
       </c>
       <c r="F17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -14369,7 +14348,7 @@
         <v>346</v>
       </c>
       <c r="F18" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -14389,7 +14368,7 @@
         <v>360</v>
       </c>
       <c r="F19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -14409,7 +14388,7 @@
         <v>362</v>
       </c>
       <c r="F20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -14429,7 +14408,7 @@
         <v>364</v>
       </c>
       <c r="F21" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -14449,7 +14428,7 @@
         <v>364</v>
       </c>
       <c r="F22" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -14469,7 +14448,7 @@
         <v>358</v>
       </c>
       <c r="F23" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -14489,7 +14468,7 @@
         <v>352</v>
       </c>
       <c r="F24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -14509,7 +14488,7 @@
         <v>329</v>
       </c>
       <c r="F25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -14529,7 +14508,7 @@
         <v>368</v>
       </c>
       <c r="F26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -14549,7 +14528,7 @@
         <v>368</v>
       </c>
       <c r="F27" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -14569,7 +14548,7 @@
         <v>368</v>
       </c>
       <c r="F28" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -14589,7 +14568,7 @@
         <v>329</v>
       </c>
       <c r="F29" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -14609,7 +14588,7 @@
         <v>341</v>
       </c>
       <c r="F30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -14629,7 +14608,7 @@
         <v>341</v>
       </c>
       <c r="F31" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -14649,7 +14628,7 @@
         <v>329</v>
       </c>
       <c r="F32" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -14669,7 +14648,7 @@
         <v>341</v>
       </c>
       <c r="F33" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -14689,7 +14668,7 @@
         <v>341</v>
       </c>
       <c r="F34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -14729,7 +14708,7 @@
         <v>349</v>
       </c>
       <c r="F36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -14749,7 +14728,7 @@
         <v>346</v>
       </c>
       <c r="F37" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -14769,7 +14748,7 @@
         <v>346</v>
       </c>
       <c r="F38" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -14789,7 +14768,7 @@
         <v>360</v>
       </c>
       <c r="F39" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -14809,7 +14788,7 @@
         <v>364</v>
       </c>
       <c r="F40" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -14849,7 +14828,7 @@
         <v>329</v>
       </c>
       <c r="F42" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -14869,7 +14848,7 @@
         <v>372</v>
       </c>
       <c r="F43" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -14909,7 +14888,7 @@
         <v>358</v>
       </c>
       <c r="F45" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -14929,7 +14908,7 @@
         <v>341</v>
       </c>
       <c r="F46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -14949,7 +14928,7 @@
         <v>341</v>
       </c>
       <c r="F47" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -14969,7 +14948,7 @@
         <v>341</v>
       </c>
       <c r="F48" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -14989,7 +14968,7 @@
         <v>374</v>
       </c>
       <c r="F49" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -15009,7 +14988,7 @@
         <v>376</v>
       </c>
       <c r="F50" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
@@ -15029,7 +15008,7 @@
         <v>378</v>
       </c>
       <c r="F51" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -15049,7 +15028,7 @@
         <v>380</v>
       </c>
       <c r="F52" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -15069,7 +15048,7 @@
         <v>329</v>
       </c>
       <c r="F53" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
@@ -15089,7 +15068,7 @@
         <v>368</v>
       </c>
       <c r="F54" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
@@ -15109,7 +15088,7 @@
         <v>368</v>
       </c>
       <c r="F55" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -15129,7 +15108,7 @@
         <v>329</v>
       </c>
       <c r="F56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
@@ -15149,7 +15128,7 @@
         <v>341</v>
       </c>
       <c r="F57" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -15169,7 +15148,7 @@
         <v>341</v>
       </c>
       <c r="F58" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
@@ -15189,7 +15168,7 @@
         <v>368</v>
       </c>
       <c r="F59" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
@@ -15229,7 +15208,7 @@
         <v>349</v>
       </c>
       <c r="F61" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
@@ -15289,7 +15268,7 @@
         <v>362</v>
       </c>
       <c r="F64" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -15309,7 +15288,7 @@
         <v>341</v>
       </c>
       <c r="F65" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -15329,7 +15308,7 @@
         <v>341</v>
       </c>
       <c r="F66" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
@@ -15349,7 +15328,7 @@
         <v>341</v>
       </c>
       <c r="F67" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
@@ -15369,7 +15348,7 @@
         <v>380</v>
       </c>
       <c r="F68" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
@@ -15424,9 +15403,9 @@
           </x14:formula1>
           <xm:sqref>D71:D97</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AB3E955A-C7A2-B24B-A8FF-4B286E4B6D6A}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{94FBFC19-8399-B845-9136-8ADD0ABA1617}">
           <x14:formula1>
-            <xm:f>ref!$A$15:$A$19</xm:f>
+            <xm:f>ref!$B$15:$B$17</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F70</xm:sqref>
         </x14:dataValidation>
@@ -15462,7 +15441,7 @@
         <v>214</v>
       </c>
       <c r="F1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -15483,7 +15462,7 @@
         <v>386</v>
       </c>
       <c r="F2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -15504,7 +15483,7 @@
         <v>349</v>
       </c>
       <c r="F3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -15525,7 +15504,7 @@
         <v>372</v>
       </c>
       <c r="F4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -15609,7 +15588,7 @@
         <v>387</v>
       </c>
       <c r="F8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -15651,7 +15630,7 @@
         <v>402</v>
       </c>
       <c r="F10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -15672,7 +15651,7 @@
         <v>402</v>
       </c>
       <c r="F11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -15714,7 +15693,7 @@
         <v>388</v>
       </c>
       <c r="F13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -15735,7 +15714,7 @@
         <v>387</v>
       </c>
       <c r="F14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -15756,7 +15735,7 @@
         <v>404</v>
       </c>
       <c r="F15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -15840,7 +15819,7 @@
         <v>388</v>
       </c>
       <c r="F19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -15861,7 +15840,7 @@
         <v>387</v>
       </c>
       <c r="F20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -15924,7 +15903,7 @@
         <v>399</v>
       </c>
       <c r="F23" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -15945,7 +15924,7 @@
         <v>388</v>
       </c>
       <c r="F24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -15966,7 +15945,7 @@
         <v>390</v>
       </c>
       <c r="F25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -15987,7 +15966,7 @@
         <v>392</v>
       </c>
       <c r="F26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -16008,7 +15987,7 @@
         <v>392</v>
       </c>
       <c r="F27" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -16029,7 +16008,7 @@
         <v>209</v>
       </c>
       <c r="F28" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -16071,7 +16050,7 @@
         <v>402</v>
       </c>
       <c r="F30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -16092,7 +16071,7 @@
         <v>388</v>
       </c>
       <c r="F31" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -16113,7 +16092,7 @@
         <v>388</v>
       </c>
       <c r="F32" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -16197,7 +16176,7 @@
         <v>387</v>
       </c>
       <c r="F36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -16260,7 +16239,7 @@
         <v>402</v>
       </c>
       <c r="F39" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -16302,7 +16281,7 @@
         <v>388</v>
       </c>
       <c r="F41" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -16323,7 +16302,7 @@
         <v>215</v>
       </c>
       <c r="F42" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -16344,7 +16323,7 @@
         <v>215</v>
       </c>
       <c r="F43" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -16386,7 +16365,7 @@
         <v>415</v>
       </c>
       <c r="F45" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -16407,7 +16386,7 @@
         <v>417</v>
       </c>
       <c r="F46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -16428,7 +16407,7 @@
         <v>215</v>
       </c>
       <c r="F47" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -16449,7 +16428,7 @@
         <v>215</v>
       </c>
       <c r="F48" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -16491,7 +16470,7 @@
         <v>415</v>
       </c>
       <c r="F50" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
@@ -16512,7 +16491,7 @@
         <v>417</v>
       </c>
       <c r="F51" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -16533,9 +16512,9 @@
           </x14:formula1>
           <xm:sqref>D52:D81</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8C646DD4-1D20-1E42-B17F-2299506629B3}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{32C82CE5-73E4-1B42-B32B-F29CE150E51A}">
           <x14:formula1>
-            <xm:f>ref!$A$15:$A$19</xm:f>
+            <xm:f>ref!$B$15:$B$17</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F51</xm:sqref>
         </x14:dataValidation>
@@ -16845,7 +16824,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B1" t="s">
         <v>319</v>
@@ -16854,10 +16833,10 @@
         <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -16874,7 +16853,7 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -16891,7 +16870,7 @@
         <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -16908,7 +16887,7 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -16925,7 +16904,7 @@
         <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -16942,7 +16921,7 @@
         <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -16959,7 +16938,7 @@
         <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -16976,7 +16955,7 @@
         <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -16993,7 +16972,7 @@
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -17010,7 +16989,7 @@
         <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -17027,7 +17006,7 @@
         <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -17044,7 +17023,7 @@
         <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -17055,13 +17034,13 @@
         <v>315</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -17072,13 +17051,13 @@
         <v>315</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D14" t="s">
         <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -17089,13 +17068,13 @@
         <v>315</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D15" t="s">
         <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -17106,13 +17085,13 @@
         <v>315</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D16" t="s">
         <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -17123,13 +17102,13 @@
         <v>315</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -17140,13 +17119,13 @@
         <v>315</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D18" t="s">
         <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -17157,13 +17136,13 @@
         <v>315</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D19" t="s">
         <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -17174,13 +17153,13 @@
         <v>315</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -17191,13 +17170,13 @@
         <v>315</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D21" t="s">
         <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -17208,13 +17187,13 @@
         <v>315</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D22" t="s">
         <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -17225,13 +17204,13 @@
         <v>315</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D23" t="s">
         <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -17248,7 +17227,7 @@
         <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -17265,7 +17244,7 @@
         <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -17282,7 +17261,7 @@
         <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -17299,7 +17278,7 @@
         <v>69</v>
       </c>
       <c r="E27" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -17316,7 +17295,7 @@
         <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -17333,7 +17312,7 @@
         <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -17350,7 +17329,7 @@
         <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -17367,7 +17346,7 @@
         <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -17384,7 +17363,7 @@
         <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -17401,7 +17380,7 @@
         <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -17418,7 +17397,7 @@
         <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17429,13 +17408,13 @@
         <v>316</v>
       </c>
       <c r="C35" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D35" t="s">
         <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -17446,13 +17425,13 @@
         <v>316</v>
       </c>
       <c r="C36" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D36" t="s">
         <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -17463,13 +17442,13 @@
         <v>316</v>
       </c>
       <c r="C37" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D37" t="s">
         <v>65</v>
       </c>
       <c r="E37" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -17480,13 +17459,13 @@
         <v>316</v>
       </c>
       <c r="C38" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D38" t="s">
         <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -17497,13 +17476,13 @@
         <v>316</v>
       </c>
       <c r="C39" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D39" t="s">
         <v>71</v>
       </c>
       <c r="E39" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -17514,13 +17493,13 @@
         <v>316</v>
       </c>
       <c r="C40" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D40" t="s">
         <v>78</v>
       </c>
       <c r="E40" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -17531,13 +17510,13 @@
         <v>316</v>
       </c>
       <c r="C41" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D41" t="s">
         <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -17548,13 +17527,13 @@
         <v>316</v>
       </c>
       <c r="C42" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -17565,13 +17544,13 @@
         <v>316</v>
       </c>
       <c r="C43" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D43" t="s">
         <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -17582,13 +17561,13 @@
         <v>316</v>
       </c>
       <c r="C44" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D44" t="s">
         <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -17599,13 +17578,13 @@
         <v>316</v>
       </c>
       <c r="C45" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D45" t="s">
         <v>97</v>
       </c>
       <c r="E45" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -17622,7 +17601,7 @@
         <v>58</v>
       </c>
       <c r="E46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -17639,7 +17618,7 @@
         <v>60</v>
       </c>
       <c r="E47" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -17656,7 +17635,7 @@
         <v>65</v>
       </c>
       <c r="E48" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -17673,7 +17652,7 @@
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -17690,7 +17669,7 @@
         <v>71</v>
       </c>
       <c r="E50" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -17707,7 +17686,7 @@
         <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -17724,7 +17703,7 @@
         <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -17741,7 +17720,7 @@
         <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -17758,7 +17737,7 @@
         <v>91</v>
       </c>
       <c r="E54" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -17775,7 +17754,7 @@
         <v>94</v>
       </c>
       <c r="E55" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -17792,7 +17771,7 @@
         <v>97</v>
       </c>
       <c r="E56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -17809,7 +17788,7 @@
         <v>58</v>
       </c>
       <c r="E57" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -17826,7 +17805,7 @@
         <v>60</v>
       </c>
       <c r="E58" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -17843,7 +17822,7 @@
         <v>65</v>
       </c>
       <c r="E59" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -17860,7 +17839,7 @@
         <v>69</v>
       </c>
       <c r="E60" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -17877,7 +17856,7 @@
         <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -17894,7 +17873,7 @@
         <v>78</v>
       </c>
       <c r="E62" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -17911,7 +17890,7 @@
         <v>83</v>
       </c>
       <c r="E63" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -17928,7 +17907,7 @@
         <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -17945,7 +17924,7 @@
         <v>91</v>
       </c>
       <c r="E65" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -17962,7 +17941,7 @@
         <v>94</v>
       </c>
       <c r="E66" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -17979,7 +17958,7 @@
         <v>97</v>
       </c>
       <c r="E67" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -17996,7 +17975,7 @@
         <v>58</v>
       </c>
       <c r="E68" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -18013,7 +17992,7 @@
         <v>60</v>
       </c>
       <c r="E69" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -18030,7 +18009,7 @@
         <v>65</v>
       </c>
       <c r="E70" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -18047,7 +18026,7 @@
         <v>69</v>
       </c>
       <c r="E71" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -18064,7 +18043,7 @@
         <v>71</v>
       </c>
       <c r="E72" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -18081,7 +18060,7 @@
         <v>78</v>
       </c>
       <c r="E73" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -18098,7 +18077,7 @@
         <v>83</v>
       </c>
       <c r="E74" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -18115,7 +18094,7 @@
         <v>17</v>
       </c>
       <c r="E75" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -18132,7 +18111,7 @@
         <v>91</v>
       </c>
       <c r="E76" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -18149,7 +18128,7 @@
         <v>94</v>
       </c>
       <c r="E77" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -18166,7 +18145,7 @@
         <v>97</v>
       </c>
       <c r="E78" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -18177,13 +18156,13 @@
         <v>316</v>
       </c>
       <c r="C79" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D79" t="s">
         <v>58</v>
       </c>
       <c r="E79" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -18194,13 +18173,13 @@
         <v>316</v>
       </c>
       <c r="C80" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D80" t="s">
         <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -18211,13 +18190,13 @@
         <v>316</v>
       </c>
       <c r="C81" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
       </c>
       <c r="E81" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -18228,13 +18207,13 @@
         <v>316</v>
       </c>
       <c r="C82" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D82" t="s">
         <v>69</v>
       </c>
       <c r="E82" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -18245,13 +18224,13 @@
         <v>316</v>
       </c>
       <c r="C83" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D83" t="s">
         <v>71</v>
       </c>
       <c r="E83" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -18262,13 +18241,13 @@
         <v>316</v>
       </c>
       <c r="C84" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D84" t="s">
         <v>78</v>
       </c>
       <c r="E84" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -18279,13 +18258,13 @@
         <v>316</v>
       </c>
       <c r="C85" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D85" t="s">
         <v>83</v>
       </c>
       <c r="E85" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -18296,13 +18275,13 @@
         <v>316</v>
       </c>
       <c r="C86" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D86" t="s">
         <v>17</v>
       </c>
       <c r="E86" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -18313,13 +18292,13 @@
         <v>316</v>
       </c>
       <c r="C87" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D87" t="s">
         <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -18330,13 +18309,13 @@
         <v>316</v>
       </c>
       <c r="C88" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D88" t="s">
         <v>94</v>
       </c>
       <c r="E88" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -18347,13 +18326,13 @@
         <v>316</v>
       </c>
       <c r="C89" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D89" t="s">
         <v>97</v>
       </c>
       <c r="E89" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -18364,13 +18343,13 @@
         <v>316</v>
       </c>
       <c r="C90" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D90" t="s">
         <v>58</v>
       </c>
       <c r="E90" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -18381,13 +18360,13 @@
         <v>316</v>
       </c>
       <c r="C91" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D91" t="s">
         <v>60</v>
       </c>
       <c r="E91" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -18398,13 +18377,13 @@
         <v>316</v>
       </c>
       <c r="C92" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D92" t="s">
         <v>65</v>
       </c>
       <c r="E92" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -18415,13 +18394,13 @@
         <v>316</v>
       </c>
       <c r="C93" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D93" t="s">
         <v>69</v>
       </c>
       <c r="E93" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -18432,13 +18411,13 @@
         <v>316</v>
       </c>
       <c r="C94" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D94" t="s">
         <v>71</v>
       </c>
       <c r="E94" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -18449,13 +18428,13 @@
         <v>316</v>
       </c>
       <c r="C95" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D95" t="s">
         <v>78</v>
       </c>
       <c r="E95" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -18466,13 +18445,13 @@
         <v>316</v>
       </c>
       <c r="C96" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D96" t="s">
         <v>83</v>
       </c>
       <c r="E96" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -18483,13 +18462,13 @@
         <v>316</v>
       </c>
       <c r="C97" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D97" t="s">
         <v>17</v>
       </c>
       <c r="E97" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -18500,13 +18479,13 @@
         <v>316</v>
       </c>
       <c r="C98" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D98" t="s">
         <v>91</v>
       </c>
       <c r="E98" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -18517,13 +18496,13 @@
         <v>316</v>
       </c>
       <c r="C99" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D99" t="s">
         <v>94</v>
       </c>
       <c r="E99" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -18534,13 +18513,13 @@
         <v>316</v>
       </c>
       <c r="C100" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D100" t="s">
         <v>97</v>
       </c>
       <c r="E100" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -18557,7 +18536,7 @@
         <v>58</v>
       </c>
       <c r="E101" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -18574,7 +18553,7 @@
         <v>60</v>
       </c>
       <c r="E102" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -18591,7 +18570,7 @@
         <v>65</v>
       </c>
       <c r="E103" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -18608,7 +18587,7 @@
         <v>69</v>
       </c>
       <c r="E104" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -18625,7 +18604,7 @@
         <v>71</v>
       </c>
       <c r="E105" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -18642,7 +18621,7 @@
         <v>78</v>
       </c>
       <c r="E106" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -18659,7 +18638,7 @@
         <v>83</v>
       </c>
       <c r="E107" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -18676,7 +18655,7 @@
         <v>17</v>
       </c>
       <c r="E108" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -18693,7 +18672,7 @@
         <v>91</v>
       </c>
       <c r="E109" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -18710,7 +18689,7 @@
         <v>94</v>
       </c>
       <c r="E110" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -18727,7 +18706,7 @@
         <v>97</v>
       </c>
       <c r="E111" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -18744,7 +18723,7 @@
         <v>58</v>
       </c>
       <c r="E112" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -18761,7 +18740,7 @@
         <v>60</v>
       </c>
       <c r="E113" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -18778,7 +18757,7 @@
         <v>65</v>
       </c>
       <c r="E114" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -18795,7 +18774,7 @@
         <v>69</v>
       </c>
       <c r="E115" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -18812,7 +18791,7 @@
         <v>71</v>
       </c>
       <c r="E116" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -18829,7 +18808,7 @@
         <v>78</v>
       </c>
       <c r="E117" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -18846,7 +18825,7 @@
         <v>83</v>
       </c>
       <c r="E118" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -18863,7 +18842,7 @@
         <v>17</v>
       </c>
       <c r="E119" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -18880,7 +18859,7 @@
         <v>91</v>
       </c>
       <c r="E120" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -18897,7 +18876,7 @@
         <v>94</v>
       </c>
       <c r="E121" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -18914,7 +18893,7 @@
         <v>97</v>
       </c>
       <c r="E122" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -18931,7 +18910,7 @@
         <v>58</v>
       </c>
       <c r="E123" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -18948,7 +18927,7 @@
         <v>60</v>
       </c>
       <c r="E124" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -18965,7 +18944,7 @@
         <v>65</v>
       </c>
       <c r="E125" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -18982,7 +18961,7 @@
         <v>69</v>
       </c>
       <c r="E126" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -18999,7 +18978,7 @@
         <v>71</v>
       </c>
       <c r="E127" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -19016,7 +18995,7 @@
         <v>78</v>
       </c>
       <c r="E128" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -19033,7 +19012,7 @@
         <v>83</v>
       </c>
       <c r="E129" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -19050,7 +19029,7 @@
         <v>17</v>
       </c>
       <c r="E130" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -19067,7 +19046,7 @@
         <v>91</v>
       </c>
       <c r="E131" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -19084,7 +19063,7 @@
         <v>94</v>
       </c>
       <c r="E132" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -19101,7 +19080,7 @@
         <v>97</v>
       </c>
       <c r="E133" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
